--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131252370</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131252377</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131252402</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>131252359</v>
       </c>
       <c r="B5" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>131252408</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>131252303</v>
       </c>
       <c r="B7" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,40 +1265,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131252319</v>
+        <v>131252348</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1308,10 +1309,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431343</v>
+        <v>431502</v>
       </c>
       <c r="R8" t="n">
-        <v>6779764</v>
+        <v>6779842</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,6 +1353,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1370,41 +1372,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131252348</v>
+        <v>131252319</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1414,10 +1415,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431502</v>
+        <v>431343</v>
       </c>
       <c r="R9" t="n">
-        <v>6779842</v>
+        <v>6779764</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1458,7 +1459,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1477,54 +1477,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131252343</v>
+        <v>131252400</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431557</v>
+        <v>431231</v>
       </c>
       <c r="R10" t="n">
-        <v>6779992</v>
+        <v>6779719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1556,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1584,10 +1574,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131252400</v>
+        <v>131252294</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,21 +1585,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431231</v>
+        <v>431192</v>
       </c>
       <c r="R11" t="n">
-        <v>6779719</v>
+        <v>6779695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1681,7 +1671,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131252344</v>
+        <v>131252343</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1715,7 +1705,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1725,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431546</v>
+        <v>431557</v>
       </c>
       <c r="R12" t="n">
-        <v>6779986</v>
+        <v>6779992</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,45 +1778,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131252294</v>
+        <v>131252344</v>
       </c>
       <c r="B13" t="n">
-        <v>79865</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431192</v>
+        <v>431546</v>
       </c>
       <c r="R13" t="n">
-        <v>6779695</v>
+        <v>6779986</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1866,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1992,40 +1992,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131252317</v>
+        <v>131252413</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>8440</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2035,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431356</v>
+        <v>431288</v>
       </c>
       <c r="R15" t="n">
-        <v>6779743</v>
+        <v>6779800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2079,6 +2080,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2097,45 +2099,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131252393</v>
+        <v>131252342</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431431</v>
+        <v>431644</v>
       </c>
       <c r="R16" t="n">
-        <v>6779803</v>
+        <v>6780041</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2176,6 +2187,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2194,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131252413</v>
+        <v>131252334</v>
       </c>
       <c r="B17" t="n">
-        <v>8440</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,21 +2217,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2238,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431288</v>
+        <v>431411</v>
       </c>
       <c r="R17" t="n">
-        <v>6779800</v>
+        <v>6779968</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,7 +2313,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131252342</v>
+        <v>131252350</v>
       </c>
       <c r="B18" t="n">
         <v>8451</v>
@@ -2345,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431644</v>
+        <v>431430</v>
       </c>
       <c r="R18" t="n">
-        <v>6780041</v>
+        <v>6779818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,54 +2420,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131252334</v>
+        <v>131252393</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431411</v>
+        <v>431431</v>
       </c>
       <c r="R19" t="n">
-        <v>6779968</v>
+        <v>6779803</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,7 +2499,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2518,7 +2520,7 @@
         <v>131252390</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,41 +2614,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131252350</v>
+        <v>131252317</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2656,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431430</v>
+        <v>431356</v>
       </c>
       <c r="R21" t="n">
-        <v>6779818</v>
+        <v>6779743</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,7 +2701,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>131252396</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>131252392</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131252386</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,10 +3010,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131252321</v>
+        <v>131252371</v>
       </c>
       <c r="B25" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3021,42 +3021,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431232</v>
+        <v>430998</v>
       </c>
       <c r="R25" t="n">
-        <v>6779756</v>
+        <v>6779729</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,10 +3107,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131252371</v>
+        <v>131252391</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,10 +3142,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430998</v>
+        <v>431447</v>
       </c>
       <c r="R26" t="n">
-        <v>6779729</v>
+        <v>6779876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,10 +3204,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131252391</v>
+        <v>131252381</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,16 +3233,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431447</v>
+        <v>431806</v>
       </c>
       <c r="R27" t="n">
-        <v>6779876</v>
+        <v>6780109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3291,6 +3286,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3309,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131252381</v>
+        <v>131252405</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,19 +3334,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431806</v>
+        <v>430989</v>
       </c>
       <c r="R28" t="n">
-        <v>6780109</v>
+        <v>6779656</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3385,13 +3378,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3410,10 +3407,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131252405</v>
+        <v>131252321</v>
       </c>
       <c r="B29" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3421,34 +3418,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430989</v>
+        <v>431232</v>
       </c>
       <c r="R29" t="n">
-        <v>6779656</v>
+        <v>6779756</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3481,11 +3486,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3512,41 +3512,40 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131252332</v>
+        <v>131252309</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>57883</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3556,10 +3555,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>431340</v>
+        <v>431320</v>
       </c>
       <c r="R30" t="n">
-        <v>6779936</v>
+        <v>6779926</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,7 +3599,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3619,40 +3617,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131252309</v>
+        <v>131252332</v>
       </c>
       <c r="B31" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3662,10 +3661,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>431320</v>
+        <v>431340</v>
       </c>
       <c r="R31" t="n">
-        <v>6779926</v>
+        <v>6779936</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3706,6 +3705,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>131252316</v>
       </c>
       <c r="B32" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,54 +3829,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131252346</v>
+        <v>131252403</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431434</v>
+        <v>431055</v>
       </c>
       <c r="R33" t="n">
-        <v>6779875</v>
+        <v>6779612</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,13 +3902,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3936,10 +3931,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131252325</v>
+        <v>131252384</v>
       </c>
       <c r="B34" t="n">
-        <v>79004</v>
+        <v>79248</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,37 +3942,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431743</v>
+        <v>431710</v>
       </c>
       <c r="R34" t="n">
-        <v>6780091</v>
+        <v>6780009</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4012,13 +4004,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4037,45 +4033,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131252403</v>
+        <v>131252346</v>
       </c>
       <c r="B35" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431055</v>
+        <v>431434</v>
       </c>
       <c r="R35" t="n">
-        <v>6779612</v>
+        <v>6779875</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4110,17 +4115,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4246,45 +4247,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131252384</v>
+        <v>131252357</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431710</v>
+        <v>431074</v>
       </c>
       <c r="R37" t="n">
-        <v>6780009</v>
+        <v>6779685</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4319,17 +4329,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4348,43 +4354,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131252357</v>
+        <v>131252325</v>
       </c>
       <c r="B38" t="n">
-        <v>8451</v>
+        <v>79006</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431074</v>
+        <v>431743</v>
       </c>
       <c r="R38" t="n">
-        <v>6779685</v>
+        <v>6780091</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
         <v>131252373</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4552,54 +4552,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131252339</v>
+        <v>131252372</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431754</v>
+        <v>431053</v>
       </c>
       <c r="R40" t="n">
-        <v>6780143</v>
+        <v>6779790</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4640,7 +4631,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4659,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131252372</v>
+        <v>131252387</v>
       </c>
       <c r="B41" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4694,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431053</v>
+        <v>431622</v>
       </c>
       <c r="R41" t="n">
-        <v>6779790</v>
+        <v>6780004</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4759,7 +4749,7 @@
         <v>131252311</v>
       </c>
       <c r="B42" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4861,7 +4851,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131252341</v>
+        <v>131252339</v>
       </c>
       <c r="B43" t="n">
         <v>8451</v>
@@ -4905,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431684</v>
+        <v>431754</v>
       </c>
       <c r="R43" t="n">
-        <v>6780041</v>
+        <v>6780143</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,45 +4958,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131252387</v>
+        <v>131252341</v>
       </c>
       <c r="B44" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431622</v>
+        <v>431684</v>
       </c>
       <c r="R44" t="n">
-        <v>6780004</v>
+        <v>6780041</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5047,6 +5046,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5065,54 +5065,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131252340</v>
+        <v>131252399</v>
       </c>
       <c r="B45" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431705</v>
+        <v>431257</v>
       </c>
       <c r="R45" t="n">
-        <v>6779985</v>
+        <v>6779698</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5153,7 +5144,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5175,7 +5165,7 @@
         <v>131252313</v>
       </c>
       <c r="B46" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5277,7 +5267,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131252336</v>
+        <v>131252340</v>
       </c>
       <c r="B47" t="n">
         <v>8451</v>
@@ -5311,7 +5301,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5321,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431610</v>
+        <v>431705</v>
       </c>
       <c r="R47" t="n">
-        <v>6780067</v>
+        <v>6779985</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5384,45 +5374,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131252399</v>
+        <v>131252336</v>
       </c>
       <c r="B48" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431257</v>
+        <v>431610</v>
       </c>
       <c r="R48" t="n">
-        <v>6779698</v>
+        <v>6780067</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,6 +5462,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>131252401</v>
       </c>
       <c r="B49" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252295</v>
+        <v>131252395</v>
       </c>
       <c r="B50" t="n">
-        <v>79836</v>
+        <v>79248</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5594,37 +5594,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431735</v>
+        <v>431310</v>
       </c>
       <c r="R50" t="n">
-        <v>6780060</v>
+        <v>6779809</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5665,7 +5662,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5684,41 +5680,40 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252337</v>
+        <v>131252322</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>57883</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -5728,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431622</v>
+        <v>431214</v>
       </c>
       <c r="R51" t="n">
-        <v>6780061</v>
+        <v>6779702</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5772,7 +5767,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5791,40 +5785,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252322</v>
+        <v>131252337</v>
       </c>
       <c r="B52" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5834,10 +5829,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431214</v>
+        <v>431622</v>
       </c>
       <c r="R52" t="n">
-        <v>6779702</v>
+        <v>6780061</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5878,6 +5873,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6110,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252395</v>
+        <v>131252295</v>
       </c>
       <c r="B55" t="n">
-        <v>79246</v>
+        <v>79838</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6121,34 +6117,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431310</v>
+        <v>431735</v>
       </c>
       <c r="R55" t="n">
-        <v>6779809</v>
+        <v>6780060</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6189,6 +6188,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>131252324</v>
       </c>
       <c r="B56" t="n">
-        <v>79004</v>
+        <v>79006</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252312</v>
+        <v>131252326</v>
       </c>
       <c r="B57" t="n">
-        <v>57881</v>
+        <v>79006</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,31 +6315,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6347,10 +6342,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431640</v>
+        <v>431339</v>
       </c>
       <c r="R57" t="n">
-        <v>6780016</v>
+        <v>6779765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6391,6 +6386,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6412,7 +6408,7 @@
         <v>131252376</v>
       </c>
       <c r="B58" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6509,7 +6505,7 @@
         <v>131252397</v>
       </c>
       <c r="B59" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6603,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131252326</v>
+        <v>131252312</v>
       </c>
       <c r="B60" t="n">
-        <v>79004</v>
+        <v>57883</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6614,26 +6610,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6641,10 +6642,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431339</v>
+        <v>431640</v>
       </c>
       <c r="R60" t="n">
-        <v>6779765</v>
+        <v>6780016</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6685,7 +6686,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>131252320</v>
       </c>
       <c r="B61" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>131252385</v>
       </c>
       <c r="B62" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6906,10 +6906,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131252301</v>
+        <v>131252398</v>
       </c>
       <c r="B63" t="n">
-        <v>58043</v>
+        <v>79248</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6917,42 +6917,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431747</v>
+        <v>431252</v>
       </c>
       <c r="R63" t="n">
-        <v>6780081</v>
+        <v>6779759</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7011,10 +7003,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131252398</v>
+        <v>131252301</v>
       </c>
       <c r="B64" t="n">
-        <v>79246</v>
+        <v>58045</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7022,34 +7014,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431252</v>
+        <v>431747</v>
       </c>
       <c r="R64" t="n">
-        <v>6779759</v>
+        <v>6780081</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7108,37 +7108,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131252302</v>
+        <v>131252328</v>
       </c>
       <c r="B65" t="n">
-        <v>91835</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7146,10 +7152,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431364</v>
+        <v>431002</v>
       </c>
       <c r="R65" t="n">
-        <v>6779943</v>
+        <v>6779756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7209,45 +7215,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131252360</v>
+        <v>131252351</v>
       </c>
       <c r="B66" t="n">
-        <v>79003</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430970</v>
+        <v>431370</v>
       </c>
       <c r="R66" t="n">
-        <v>6779700</v>
+        <v>6779803</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7288,6 +7303,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7306,7 +7322,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131252328</v>
+        <v>131252354</v>
       </c>
       <c r="B67" t="n">
         <v>8451</v>
@@ -7340,7 +7356,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7350,10 +7366,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431002</v>
+        <v>431358</v>
       </c>
       <c r="R67" t="n">
-        <v>6779756</v>
+        <v>6779744</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7413,43 +7429,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131252351</v>
+        <v>131252302</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>91837</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7457,10 +7467,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431370</v>
+        <v>431364</v>
       </c>
       <c r="R68" t="n">
-        <v>6779803</v>
+        <v>6779943</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7520,54 +7530,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131252354</v>
+        <v>131252360</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>79005</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431358</v>
+        <v>430970</v>
       </c>
       <c r="R69" t="n">
-        <v>6779744</v>
+        <v>6779700</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7608,7 +7609,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>131252374</v>
       </c>
       <c r="B70" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7724,54 +7724,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131252333</v>
+        <v>131252389</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431385</v>
+        <v>431389</v>
       </c>
       <c r="R71" t="n">
-        <v>6779961</v>
+        <v>6779928</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7812,7 +7803,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7831,10 +7821,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131252389</v>
+        <v>131252407</v>
       </c>
       <c r="B72" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7860,16 +7850,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431389</v>
+        <v>430942</v>
       </c>
       <c r="R72" t="n">
-        <v>6779928</v>
+        <v>6779693</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7910,6 +7903,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7928,10 +7922,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131252407</v>
+        <v>131252375</v>
       </c>
       <c r="B73" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7957,19 +7951,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430942</v>
+        <v>431294</v>
       </c>
       <c r="R73" t="n">
-        <v>6779693</v>
+        <v>6779898</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8010,7 +8001,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8029,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131252375</v>
+        <v>131252314</v>
       </c>
       <c r="B74" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8040,34 +8030,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431294</v>
+        <v>431448</v>
       </c>
       <c r="R74" t="n">
-        <v>6779898</v>
+        <v>6779825</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8126,40 +8124,41 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252314</v>
+        <v>131252333</v>
       </c>
       <c r="B75" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8169,10 +8168,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431448</v>
+        <v>431385</v>
       </c>
       <c r="R75" t="n">
-        <v>6779825</v>
+        <v>6779961</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,6 +8212,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8338,45 +8338,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131252406</v>
+        <v>131252349</v>
       </c>
       <c r="B77" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430975</v>
+        <v>431444</v>
       </c>
       <c r="R77" t="n">
-        <v>6779698</v>
+        <v>6779818</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8417,6 +8426,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8435,40 +8445,41 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252306</v>
+        <v>131252345</v>
       </c>
       <c r="B78" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8478,10 +8489,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430985</v>
+        <v>431376</v>
       </c>
       <c r="R78" t="n">
-        <v>6779728</v>
+        <v>6779903</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8522,6 +8533,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8540,54 +8552,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131252349</v>
+        <v>131252406</v>
       </c>
       <c r="B79" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431444</v>
+        <v>430975</v>
       </c>
       <c r="R79" t="n">
-        <v>6779818</v>
+        <v>6779698</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8628,7 +8631,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8647,41 +8649,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131252345</v>
+        <v>131252306</v>
       </c>
       <c r="B80" t="n">
-        <v>8451</v>
+        <v>57883</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8691,10 +8692,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431376</v>
+        <v>430985</v>
       </c>
       <c r="R80" t="n">
-        <v>6779903</v>
+        <v>6779728</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8735,7 +8736,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8757,7 +8757,7 @@
         <v>131252308</v>
       </c>
       <c r="B81" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>131252383</v>
       </c>
       <c r="B82" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8956,10 +8956,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131252315</v>
+        <v>131252379</v>
       </c>
       <c r="B83" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8967,42 +8967,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431370</v>
+        <v>431606</v>
       </c>
       <c r="R83" t="n">
-        <v>6779803</v>
+        <v>6780065</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9061,10 +9053,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131252379</v>
+        <v>131252404</v>
       </c>
       <c r="B84" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9096,10 +9088,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431606</v>
+        <v>431024</v>
       </c>
       <c r="R84" t="n">
-        <v>6780065</v>
+        <v>6779638</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9158,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131252404</v>
+        <v>131252380</v>
       </c>
       <c r="B85" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9193,10 +9185,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431024</v>
+        <v>431673</v>
       </c>
       <c r="R85" t="n">
-        <v>6779638</v>
+        <v>6780100</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9255,41 +9247,40 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131252335</v>
+        <v>131252315</v>
       </c>
       <c r="B86" t="n">
-        <v>8451</v>
+        <v>57883</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9299,10 +9290,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431434</v>
+        <v>431370</v>
       </c>
       <c r="R86" t="n">
-        <v>6779988</v>
+        <v>6779803</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9343,7 +9334,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9362,45 +9352,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131252380</v>
+        <v>131252335</v>
       </c>
       <c r="B87" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431673</v>
+        <v>431434</v>
       </c>
       <c r="R87" t="n">
-        <v>6780100</v>
+        <v>6779988</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9441,6 +9440,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9462,7 +9462,7 @@
         <v>131252304</v>
       </c>
       <c r="B88" t="n">
-        <v>91835</v>
+        <v>91837</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>131252323</v>
       </c>
       <c r="B89" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9665,54 +9665,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131252331</v>
+        <v>131252394</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431291</v>
+        <v>431327</v>
       </c>
       <c r="R90" t="n">
-        <v>6779892</v>
+        <v>6779796</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9753,7 +9744,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9772,7 +9762,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131252330</v>
+        <v>131252331</v>
       </c>
       <c r="B91" t="n">
         <v>8451</v>
@@ -9816,10 +9806,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431075</v>
+        <v>431291</v>
       </c>
       <c r="R91" t="n">
-        <v>6779775</v>
+        <v>6779892</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9879,45 +9869,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131252394</v>
+        <v>131252330</v>
       </c>
       <c r="B92" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431327</v>
+        <v>431075</v>
       </c>
       <c r="R92" t="n">
-        <v>6779796</v>
+        <v>6779775</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9958,6 +9957,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9976,45 +9976,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131252293</v>
+        <v>131252300</v>
       </c>
       <c r="B93" t="n">
-        <v>79865</v>
+        <v>57075</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431669</v>
+        <v>431560</v>
       </c>
       <c r="R93" t="n">
-        <v>6780050</v>
+        <v>6779996</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10073,53 +10081,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131252300</v>
+        <v>131252293</v>
       </c>
       <c r="B94" t="n">
-        <v>57073</v>
+        <v>79867</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431560</v>
+        <v>431669</v>
       </c>
       <c r="R94" t="n">
-        <v>6779996</v>
+        <v>6780050</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131252382</v>
+        <v>131252305</v>
       </c>
       <c r="B97" t="n">
-        <v>79246</v>
+        <v>91837</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10403,34 +10403,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431806</v>
+        <v>431438</v>
       </c>
       <c r="R97" t="n">
-        <v>6780050</v>
+        <v>6779872</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10471,6 +10474,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10489,54 +10493,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131252409</v>
+        <v>131252388</v>
       </c>
       <c r="B98" t="n">
-        <v>5177</v>
+        <v>79248</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431446</v>
+        <v>431442</v>
       </c>
       <c r="R98" t="n">
-        <v>6779877</v>
+        <v>6779937</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10577,7 +10572,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10596,10 +10590,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131252378</v>
+        <v>131252382</v>
       </c>
       <c r="B99" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10631,10 +10625,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431561</v>
+        <v>431806</v>
       </c>
       <c r="R99" t="n">
-        <v>6780045</v>
+        <v>6780050</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10693,10 +10687,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131252305</v>
+        <v>131252378</v>
       </c>
       <c r="B100" t="n">
-        <v>91835</v>
+        <v>79248</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10704,37 +10698,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431438</v>
+        <v>431561</v>
       </c>
       <c r="R100" t="n">
-        <v>6779872</v>
+        <v>6780045</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10775,7 +10766,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10794,45 +10784,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131252388</v>
+        <v>131252409</v>
       </c>
       <c r="B101" t="n">
-        <v>79246</v>
+        <v>5177</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431442</v>
+        <v>431446</v>
       </c>
       <c r="R101" t="n">
-        <v>6779937</v>
+        <v>6779877</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10873,6 +10872,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131252370</v>
+        <v>131252359</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430909</v>
+        <v>431017</v>
       </c>
       <c r="R2" t="n">
-        <v>6779703</v>
+        <v>6779783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131252377</v>
+        <v>131252370</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431422</v>
+        <v>430909</v>
       </c>
       <c r="R3" t="n">
-        <v>6779979</v>
+        <v>6779703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131252402</v>
+        <v>131252377</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,19 +898,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431075</v>
+        <v>431422</v>
       </c>
       <c r="R4" t="n">
-        <v>6779646</v>
+        <v>6779979</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,7 +948,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131252359</v>
+        <v>131252402</v>
       </c>
       <c r="B5" t="n">
-        <v>79005</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,34 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431017</v>
+        <v>431075</v>
       </c>
       <c r="R5" t="n">
-        <v>6779783</v>
+        <v>6779646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>131252408</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131252303</v>
+        <v>131252319</v>
       </c>
       <c r="B7" t="n">
-        <v>91837</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,26 +1175,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1202,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431783</v>
+        <v>431343</v>
       </c>
       <c r="R7" t="n">
-        <v>6780157</v>
+        <v>6779764</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,7 +1251,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1265,43 +1269,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131252348</v>
+        <v>131252303</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1309,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431502</v>
+        <v>431783</v>
       </c>
       <c r="R8" t="n">
-        <v>6779842</v>
+        <v>6780157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,40 +1370,41 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131252319</v>
+        <v>131252348</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1415,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431343</v>
+        <v>431502</v>
       </c>
       <c r="R9" t="n">
-        <v>6779764</v>
+        <v>6779842</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1458,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>131252400</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>131252294</v>
       </c>
       <c r="B11" t="n">
-        <v>79867</v>
+        <v>79868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1992,54 +1992,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131252413</v>
+        <v>131252393</v>
       </c>
       <c r="B15" t="n">
-        <v>8440</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431288</v>
+        <v>431431</v>
       </c>
       <c r="R15" t="n">
-        <v>6779800</v>
+        <v>6779803</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,7 +2071,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2099,54 +2089,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131252342</v>
+        <v>131252390</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431644</v>
+        <v>431416</v>
       </c>
       <c r="R16" t="n">
-        <v>6780041</v>
+        <v>6779884</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2187,7 +2168,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2206,41 +2186,40 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131252334</v>
+        <v>131252317</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2250,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431411</v>
+        <v>431356</v>
       </c>
       <c r="R17" t="n">
-        <v>6779968</v>
+        <v>6779743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,7 +2273,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2313,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131252350</v>
+        <v>131252413</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>8440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431430</v>
+        <v>431288</v>
       </c>
       <c r="R18" t="n">
-        <v>6779818</v>
+        <v>6779800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2420,45 +2398,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131252393</v>
+        <v>131252342</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431431</v>
+        <v>431644</v>
       </c>
       <c r="R19" t="n">
-        <v>6779803</v>
+        <v>6780041</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2499,6 +2486,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2517,45 +2505,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131252390</v>
+        <v>131252334</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431416</v>
+        <v>431411</v>
       </c>
       <c r="R20" t="n">
-        <v>6779884</v>
+        <v>6779968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2596,6 +2593,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2614,40 +2612,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131252317</v>
+        <v>131252350</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2657,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431356</v>
+        <v>431430</v>
       </c>
       <c r="R21" t="n">
-        <v>6779743</v>
+        <v>6779818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,6 +2700,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>131252396</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>131252392</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131252386</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>131252371</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>131252391</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>131252381</v>
       </c>
       <c r="B27" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>131252405</v>
       </c>
       <c r="B28" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>131252321</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>131252309</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131252316</v>
+        <v>131252403</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3735,42 +3735,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431357</v>
+        <v>431055</v>
       </c>
       <c r="R32" t="n">
-        <v>6779763</v>
+        <v>6779612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3803,6 +3795,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3829,10 +3826,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131252403</v>
+        <v>131252384</v>
       </c>
       <c r="B33" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3864,10 +3861,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431055</v>
+        <v>431710</v>
       </c>
       <c r="R33" t="n">
-        <v>6779612</v>
+        <v>6780009</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3904,7 +3901,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3931,45 +3928,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131252384</v>
+        <v>131252346</v>
       </c>
       <c r="B34" t="n">
-        <v>79248</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431710</v>
+        <v>431434</v>
       </c>
       <c r="R34" t="n">
-        <v>6780009</v>
+        <v>6779875</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4004,17 +4010,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4033,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131252346</v>
+        <v>131252414</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>8440</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,21 +4046,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4077,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431434</v>
+        <v>431245</v>
       </c>
       <c r="R35" t="n">
-        <v>6779875</v>
+        <v>6779803</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4140,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131252414</v>
+        <v>131252357</v>
       </c>
       <c r="B36" t="n">
-        <v>8440</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4184,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431245</v>
+        <v>431074</v>
       </c>
       <c r="R36" t="n">
-        <v>6779803</v>
+        <v>6779685</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,41 +4249,40 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131252357</v>
+        <v>131252316</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4291,10 +4292,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431074</v>
+        <v>431357</v>
       </c>
       <c r="R37" t="n">
-        <v>6779685</v>
+        <v>6779763</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4335,7 +4336,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>131252325</v>
       </c>
       <c r="B38" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>131252373</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>131252372</v>
       </c>
       <c r="B40" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>131252387</v>
       </c>
       <c r="B41" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>131252311</v>
       </c>
       <c r="B42" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5065,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131252399</v>
+        <v>131252313</v>
       </c>
       <c r="B45" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,34 +5076,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431257</v>
+        <v>431580</v>
       </c>
       <c r="R45" t="n">
-        <v>6779698</v>
+        <v>6779970</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5162,10 +5170,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131252313</v>
+        <v>131252399</v>
       </c>
       <c r="B46" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5173,42 +5181,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431580</v>
+        <v>431257</v>
       </c>
       <c r="R46" t="n">
-        <v>6779970</v>
+        <v>6779698</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131252401</v>
+        <v>131252322</v>
       </c>
       <c r="B49" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,34 +5492,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431082</v>
+        <v>431214</v>
       </c>
       <c r="R49" t="n">
-        <v>6779651</v>
+        <v>6779702</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5552,11 +5560,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5583,45 +5586,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252395</v>
+        <v>131252337</v>
       </c>
       <c r="B50" t="n">
-        <v>79248</v>
+        <v>8451</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431310</v>
+        <v>431622</v>
       </c>
       <c r="R50" t="n">
-        <v>6779809</v>
+        <v>6780061</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5662,6 +5674,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5680,40 +5693,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252322</v>
+        <v>131252352</v>
       </c>
       <c r="B51" t="n">
-        <v>57883</v>
+        <v>8451</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -5723,10 +5737,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431214</v>
+        <v>431374</v>
       </c>
       <c r="R51" t="n">
-        <v>6779702</v>
+        <v>6779783</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5767,6 +5781,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5785,7 +5800,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252337</v>
+        <v>131252355</v>
       </c>
       <c r="B52" t="n">
         <v>8451</v>
@@ -5829,10 +5844,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431622</v>
+        <v>431356</v>
       </c>
       <c r="R52" t="n">
-        <v>6780061</v>
+        <v>6779743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5892,54 +5907,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252352</v>
+        <v>131252401</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431374</v>
+        <v>431082</v>
       </c>
       <c r="R53" t="n">
-        <v>6779783</v>
+        <v>6779651</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5974,13 +5980,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5999,54 +6009,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252355</v>
+        <v>131252395</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431356</v>
+        <v>431310</v>
       </c>
       <c r="R54" t="n">
-        <v>6779743</v>
+        <v>6779809</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6087,7 +6088,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6106,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252295</v>
+        <v>131252324</v>
       </c>
       <c r="B55" t="n">
-        <v>79838</v>
+        <v>79007</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6117,37 +6117,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431735</v>
+        <v>431015</v>
       </c>
       <c r="R55" t="n">
-        <v>6780060</v>
+        <v>6779783</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6188,7 +6185,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6207,10 +6203,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252324</v>
+        <v>131252295</v>
       </c>
       <c r="B56" t="n">
-        <v>79006</v>
+        <v>79839</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6218,34 +6214,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431015</v>
+        <v>431735</v>
       </c>
       <c r="R56" t="n">
-        <v>6779783</v>
+        <v>6780060</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6286,6 +6285,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252326</v>
+        <v>131252312</v>
       </c>
       <c r="B57" t="n">
-        <v>79006</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,26 +6315,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6342,10 +6347,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431339</v>
+        <v>431640</v>
       </c>
       <c r="R57" t="n">
-        <v>6779765</v>
+        <v>6780016</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6386,7 +6391,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6405,10 +6409,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131252376</v>
+        <v>131252320</v>
       </c>
       <c r="B58" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,34 +6420,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431316</v>
+        <v>431254</v>
       </c>
       <c r="R58" t="n">
-        <v>6779925</v>
+        <v>6779775</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,10 +6514,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131252397</v>
+        <v>131252376</v>
       </c>
       <c r="B59" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6537,10 +6549,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431280</v>
+        <v>431316</v>
       </c>
       <c r="R59" t="n">
-        <v>6779815</v>
+        <v>6779925</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6599,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131252312</v>
+        <v>131252397</v>
       </c>
       <c r="B60" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,42 +6622,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431640</v>
+        <v>431280</v>
       </c>
       <c r="R60" t="n">
-        <v>6780016</v>
+        <v>6779815</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6704,10 +6708,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131252320</v>
+        <v>131252326</v>
       </c>
       <c r="B61" t="n">
-        <v>57883</v>
+        <v>79007</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6715,31 +6719,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6747,10 +6746,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431254</v>
+        <v>431339</v>
       </c>
       <c r="R61" t="n">
-        <v>6779775</v>
+        <v>6779765</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6791,6 +6790,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>131252385</v>
       </c>
       <c r="B62" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>131252398</v>
       </c>
       <c r="B63" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>131252301</v>
       </c>
       <c r="B64" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7108,54 +7108,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131252328</v>
+        <v>131252360</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>79006</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431002</v>
+        <v>430970</v>
       </c>
       <c r="R65" t="n">
-        <v>6779756</v>
+        <v>6779700</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7196,7 +7187,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7215,43 +7205,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131252351</v>
+        <v>131252302</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>91838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7259,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431370</v>
+        <v>431364</v>
       </c>
       <c r="R66" t="n">
-        <v>6779803</v>
+        <v>6779943</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7322,7 +7306,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131252354</v>
+        <v>131252328</v>
       </c>
       <c r="B67" t="n">
         <v>8451</v>
@@ -7356,7 +7340,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7366,10 +7350,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431358</v>
+        <v>431002</v>
       </c>
       <c r="R67" t="n">
-        <v>6779744</v>
+        <v>6779756</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7429,37 +7413,43 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131252302</v>
+        <v>131252351</v>
       </c>
       <c r="B68" t="n">
-        <v>91837</v>
+        <v>8451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7467,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431364</v>
+        <v>431370</v>
       </c>
       <c r="R68" t="n">
-        <v>6779943</v>
+        <v>6779803</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7530,45 +7520,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131252360</v>
+        <v>131252354</v>
       </c>
       <c r="B69" t="n">
-        <v>79005</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430970</v>
+        <v>431358</v>
       </c>
       <c r="R69" t="n">
-        <v>6779700</v>
+        <v>6779744</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7609,6 +7608,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>131252374</v>
       </c>
       <c r="B70" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>131252389</v>
       </c>
       <c r="B71" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>131252407</v>
       </c>
       <c r="B72" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>131252375</v>
       </c>
       <c r="B73" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>131252314</v>
       </c>
       <c r="B74" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8231,54 +8231,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131252347</v>
+        <v>131252406</v>
       </c>
       <c r="B76" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431446</v>
+        <v>430975</v>
       </c>
       <c r="R76" t="n">
-        <v>6779877</v>
+        <v>6779698</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8319,7 +8310,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8338,41 +8328,40 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131252349</v>
+        <v>131252306</v>
       </c>
       <c r="B77" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8382,10 +8371,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431444</v>
+        <v>430985</v>
       </c>
       <c r="R77" t="n">
-        <v>6779818</v>
+        <v>6779728</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8426,7 +8415,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8445,41 +8433,40 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252345</v>
+        <v>131252308</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8489,10 +8476,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431376</v>
+        <v>431243</v>
       </c>
       <c r="R78" t="n">
-        <v>6779903</v>
+        <v>6779888</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8533,7 +8520,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8552,45 +8538,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131252406</v>
+        <v>131252347</v>
       </c>
       <c r="B79" t="n">
-        <v>79248</v>
+        <v>8451</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430975</v>
+        <v>431446</v>
       </c>
       <c r="R79" t="n">
-        <v>6779698</v>
+        <v>6779877</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,6 +8626,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8649,40 +8645,41 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131252306</v>
+        <v>131252349</v>
       </c>
       <c r="B80" t="n">
-        <v>57883</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8692,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430985</v>
+        <v>431444</v>
       </c>
       <c r="R80" t="n">
-        <v>6779728</v>
+        <v>6779818</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8736,6 +8733,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8754,40 +8752,41 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131252308</v>
+        <v>131252345</v>
       </c>
       <c r="B81" t="n">
-        <v>57883</v>
+        <v>8451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8797,10 +8796,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431243</v>
+        <v>431376</v>
       </c>
       <c r="R81" t="n">
-        <v>6779888</v>
+        <v>6779903</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8841,6 +8840,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>131252383</v>
       </c>
       <c r="B82" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>131252379</v>
       </c>
       <c r="B83" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>131252404</v>
       </c>
       <c r="B84" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>131252380</v>
       </c>
       <c r="B85" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>131252315</v>
       </c>
       <c r="B86" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9459,10 +9459,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131252304</v>
+        <v>131252323</v>
       </c>
       <c r="B88" t="n">
-        <v>91837</v>
+        <v>57884</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9470,26 +9470,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9497,10 +9502,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431613</v>
+        <v>431150</v>
       </c>
       <c r="R88" t="n">
-        <v>6780015</v>
+        <v>6779694</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9541,7 +9546,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9560,10 +9564,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131252323</v>
+        <v>131252304</v>
       </c>
       <c r="B89" t="n">
-        <v>57883</v>
+        <v>91838</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9571,31 +9575,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9603,10 +9602,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431150</v>
+        <v>431613</v>
       </c>
       <c r="R89" t="n">
-        <v>6779694</v>
+        <v>6780015</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9647,6 +9646,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>131252394</v>
       </c>
       <c r="B90" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9976,53 +9976,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131252300</v>
+        <v>131252293</v>
       </c>
       <c r="B93" t="n">
-        <v>57075</v>
+        <v>79868</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431560</v>
+        <v>431669</v>
       </c>
       <c r="R93" t="n">
-        <v>6779996</v>
+        <v>6780050</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10081,45 +10073,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131252293</v>
+        <v>131252300</v>
       </c>
       <c r="B94" t="n">
-        <v>79867</v>
+        <v>57076</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431669</v>
+        <v>431560</v>
       </c>
       <c r="R94" t="n">
-        <v>6780050</v>
+        <v>6779996</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131252353</v>
+        <v>131252409</v>
       </c>
       <c r="B96" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10296,21 +10296,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10319,7 +10319,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10329,10 +10329,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431372</v>
+        <v>431446</v>
       </c>
       <c r="R96" t="n">
-        <v>6779775</v>
+        <v>6779877</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131252305</v>
+        <v>131252382</v>
       </c>
       <c r="B97" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10403,37 +10403,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431438</v>
+        <v>431806</v>
       </c>
       <c r="R97" t="n">
-        <v>6779872</v>
+        <v>6780050</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10474,7 +10471,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10493,10 +10489,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131252388</v>
+        <v>131252378</v>
       </c>
       <c r="B98" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10528,10 +10524,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431442</v>
+        <v>431561</v>
       </c>
       <c r="R98" t="n">
-        <v>6779937</v>
+        <v>6780045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10590,10 +10586,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131252382</v>
+        <v>131252388</v>
       </c>
       <c r="B99" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10625,10 +10621,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431806</v>
+        <v>431442</v>
       </c>
       <c r="R99" t="n">
-        <v>6780050</v>
+        <v>6779937</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10687,10 +10683,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131252378</v>
+        <v>131252305</v>
       </c>
       <c r="B100" t="n">
-        <v>79248</v>
+        <v>91838</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10698,34 +10694,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431561</v>
+        <v>431438</v>
       </c>
       <c r="R100" t="n">
-        <v>6780045</v>
+        <v>6779872</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10766,6 +10765,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10784,10 +10784,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131252409</v>
+        <v>131252353</v>
       </c>
       <c r="B101" t="n">
-        <v>5177</v>
+        <v>8451</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10795,21 +10795,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10818,7 +10818,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431446</v>
+        <v>431372</v>
       </c>
       <c r="R101" t="n">
-        <v>6779877</v>
+        <v>6779775</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131252359</v>
+        <v>131252377</v>
       </c>
       <c r="B2" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431017</v>
+        <v>431422</v>
       </c>
       <c r="R2" t="n">
-        <v>6779783</v>
+        <v>6779979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131252370</v>
+        <v>131252402</v>
       </c>
       <c r="B3" t="n">
         <v>79249</v>
@@ -801,16 +801,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430909</v>
+        <v>431075</v>
       </c>
       <c r="R3" t="n">
-        <v>6779703</v>
+        <v>6779646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131252377</v>
+        <v>131252359</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431422</v>
+        <v>431017</v>
       </c>
       <c r="R4" t="n">
-        <v>6779979</v>
+        <v>6779783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +970,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131252402</v>
+        <v>131252408</v>
       </c>
       <c r="B5" t="n">
         <v>79249</v>
@@ -995,19 +999,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431075</v>
+        <v>430924</v>
       </c>
       <c r="R5" t="n">
-        <v>6779646</v>
+        <v>6779690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1048,7 +1049,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131252408</v>
+        <v>131252370</v>
       </c>
       <c r="B6" t="n">
         <v>79249</v>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430924</v>
+        <v>430909</v>
       </c>
       <c r="R6" t="n">
-        <v>6779690</v>
+        <v>6779703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131252319</v>
+        <v>131252303</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,31 +1175,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1207,10 +1202,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431343</v>
+        <v>431783</v>
       </c>
       <c r="R7" t="n">
-        <v>6779764</v>
+        <v>6780157</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131252303</v>
+        <v>131252319</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1280,26 +1276,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1307,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431783</v>
+        <v>431343</v>
       </c>
       <c r="R8" t="n">
-        <v>6780157</v>
+        <v>6779764</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,7 +1352,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131252400</v>
+        <v>131252294</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431231</v>
+        <v>431192</v>
       </c>
       <c r="R10" t="n">
-        <v>6779719</v>
+        <v>6779695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,45 +1574,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131252294</v>
+        <v>131252343</v>
       </c>
       <c r="B11" t="n">
-        <v>79868</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431192</v>
+        <v>431557</v>
       </c>
       <c r="R11" t="n">
-        <v>6779695</v>
+        <v>6779992</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1662,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1671,7 +1681,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131252343</v>
+        <v>131252344</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1705,7 +1715,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1715,10 +1725,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431557</v>
+        <v>431546</v>
       </c>
       <c r="R12" t="n">
-        <v>6779992</v>
+        <v>6779986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,7 +1788,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131252344</v>
+        <v>131252358</v>
       </c>
       <c r="B13" t="n">
         <v>8451</v>
@@ -1812,7 +1822,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1822,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431546</v>
+        <v>431077</v>
       </c>
       <c r="R13" t="n">
-        <v>6779986</v>
+        <v>6779648</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,54 +1895,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131252358</v>
+        <v>131252400</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431077</v>
+        <v>431231</v>
       </c>
       <c r="R14" t="n">
-        <v>6779648</v>
+        <v>6779719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,7 +1974,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131252393</v>
+        <v>131252317</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,34 +2003,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431431</v>
+        <v>431356</v>
       </c>
       <c r="R15" t="n">
-        <v>6779803</v>
+        <v>6779743</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,40 +2194,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131252317</v>
+        <v>131252413</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>8440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2229,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431356</v>
+        <v>431288</v>
       </c>
       <c r="R17" t="n">
-        <v>6779743</v>
+        <v>6779800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,6 +2282,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2291,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131252413</v>
+        <v>131252342</v>
       </c>
       <c r="B18" t="n">
-        <v>8440</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2312,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2335,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431288</v>
+        <v>431644</v>
       </c>
       <c r="R18" t="n">
-        <v>6779800</v>
+        <v>6780041</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,7 +2408,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131252342</v>
+        <v>131252334</v>
       </c>
       <c r="B19" t="n">
         <v>8451</v>
@@ -2442,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431644</v>
+        <v>431411</v>
       </c>
       <c r="R19" t="n">
-        <v>6780041</v>
+        <v>6779968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2505,7 +2515,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131252334</v>
+        <v>131252350</v>
       </c>
       <c r="B20" t="n">
         <v>8451</v>
@@ -2549,10 +2559,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431411</v>
+        <v>431430</v>
       </c>
       <c r="R20" t="n">
-        <v>6779968</v>
+        <v>6779818</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,54 +2622,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131252350</v>
+        <v>131252393</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431430</v>
+        <v>431431</v>
       </c>
       <c r="R21" t="n">
-        <v>6779818</v>
+        <v>6779803</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,7 +2701,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131252396</v>
+        <v>131252371</v>
       </c>
       <c r="B22" t="n">
         <v>79249</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431284</v>
+        <v>430998</v>
       </c>
       <c r="R22" t="n">
-        <v>6779794</v>
+        <v>6779729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131252392</v>
+        <v>131252391</v>
       </c>
       <c r="B23" t="n">
         <v>79249</v>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431477</v>
+        <v>431447</v>
       </c>
       <c r="R23" t="n">
-        <v>6779852</v>
+        <v>6779876</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131252386</v>
+        <v>131252381</v>
       </c>
       <c r="B24" t="n">
         <v>79249</v>
@@ -2942,16 +2942,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431659</v>
+        <v>431806</v>
       </c>
       <c r="R24" t="n">
-        <v>6780052</v>
+        <v>6780109</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2992,6 +2995,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3010,7 +3014,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131252371</v>
+        <v>131252405</v>
       </c>
       <c r="B25" t="n">
         <v>79249</v>
@@ -3045,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430998</v>
+        <v>430989</v>
       </c>
       <c r="R25" t="n">
-        <v>6779729</v>
+        <v>6779656</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3081,6 +3085,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3107,10 +3116,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131252391</v>
+        <v>131252321</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3118,34 +3127,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431447</v>
+        <v>431232</v>
       </c>
       <c r="R26" t="n">
-        <v>6779876</v>
+        <v>6779756</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,7 +3221,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131252381</v>
+        <v>131252396</v>
       </c>
       <c r="B27" t="n">
         <v>79249</v>
@@ -3233,19 +3250,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431806</v>
+        <v>431284</v>
       </c>
       <c r="R27" t="n">
-        <v>6780109</v>
+        <v>6779794</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3286,7 +3300,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3305,7 +3318,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131252405</v>
+        <v>131252392</v>
       </c>
       <c r="B28" t="n">
         <v>79249</v>
@@ -3340,10 +3353,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430989</v>
+        <v>431477</v>
       </c>
       <c r="R28" t="n">
-        <v>6779656</v>
+        <v>6779852</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3376,11 +3389,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3407,10 +3415,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131252321</v>
+        <v>131252386</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3418,42 +3426,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431232</v>
+        <v>431659</v>
       </c>
       <c r="R29" t="n">
-        <v>6779756</v>
+        <v>6780052</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3724,45 +3724,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131252403</v>
+        <v>131252346</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431055</v>
+        <v>431434</v>
       </c>
       <c r="R32" t="n">
-        <v>6779612</v>
+        <v>6779875</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3797,17 +3806,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3826,45 +3831,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131252384</v>
+        <v>131252414</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>8440</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431710</v>
+        <v>431245</v>
       </c>
       <c r="R33" t="n">
-        <v>6780009</v>
+        <v>6779803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3899,17 +3913,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3928,7 +3938,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131252346</v>
+        <v>131252357</v>
       </c>
       <c r="B34" t="n">
         <v>8451</v>
@@ -3972,10 +3982,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431434</v>
+        <v>431074</v>
       </c>
       <c r="R34" t="n">
-        <v>6779875</v>
+        <v>6779685</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4035,54 +4045,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131252414</v>
+        <v>131252403</v>
       </c>
       <c r="B35" t="n">
-        <v>8440</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431245</v>
+        <v>431055</v>
       </c>
       <c r="R35" t="n">
-        <v>6779803</v>
+        <v>6779612</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4117,13 +4118,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4142,54 +4147,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131252357</v>
+        <v>131252384</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431074</v>
+        <v>431710</v>
       </c>
       <c r="R36" t="n">
-        <v>6779685</v>
+        <v>6780009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4224,13 +4220,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4249,10 +4249,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131252316</v>
+        <v>131252325</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79007</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,31 +4260,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4292,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431357</v>
+        <v>431743</v>
       </c>
       <c r="R37" t="n">
-        <v>6779763</v>
+        <v>6780091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,6 +4331,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4354,10 +4350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131252325</v>
+        <v>131252316</v>
       </c>
       <c r="B38" t="n">
-        <v>79007</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4365,26 +4361,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4392,10 +4393,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431743</v>
+        <v>431357</v>
       </c>
       <c r="R38" t="n">
-        <v>6780091</v>
+        <v>6779763</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4436,7 +4437,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5065,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131252313</v>
+        <v>131252399</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,42 +5076,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431580</v>
+        <v>431257</v>
       </c>
       <c r="R45" t="n">
-        <v>6779970</v>
+        <v>6779698</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,10 +5162,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131252399</v>
+        <v>131252313</v>
       </c>
       <c r="B46" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5181,34 +5173,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431257</v>
+        <v>431580</v>
       </c>
       <c r="R46" t="n">
-        <v>6779698</v>
+        <v>6779970</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131252322</v>
+        <v>131252401</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,42 +5492,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431214</v>
+        <v>431082</v>
       </c>
       <c r="R49" t="n">
-        <v>6779702</v>
+        <v>6779651</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5560,6 +5552,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5586,54 +5583,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252337</v>
+        <v>131252395</v>
       </c>
       <c r="B50" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431622</v>
+        <v>431310</v>
       </c>
       <c r="R50" t="n">
-        <v>6780061</v>
+        <v>6779809</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5674,7 +5662,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5693,41 +5680,40 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252352</v>
+        <v>131252322</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -5737,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431374</v>
+        <v>431214</v>
       </c>
       <c r="R51" t="n">
-        <v>6779783</v>
+        <v>6779702</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5781,7 +5767,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5800,7 +5785,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252355</v>
+        <v>131252337</v>
       </c>
       <c r="B52" t="n">
         <v>8451</v>
@@ -5844,10 +5829,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431356</v>
+        <v>431622</v>
       </c>
       <c r="R52" t="n">
-        <v>6779743</v>
+        <v>6780061</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5907,45 +5892,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252401</v>
+        <v>131252352</v>
       </c>
       <c r="B53" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431082</v>
+        <v>431374</v>
       </c>
       <c r="R53" t="n">
-        <v>6779651</v>
+        <v>6779783</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5980,17 +5974,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6009,45 +5999,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252395</v>
+        <v>131252355</v>
       </c>
       <c r="B54" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431310</v>
+        <v>431356</v>
       </c>
       <c r="R54" t="n">
-        <v>6779809</v>
+        <v>6779743</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6088,6 +6087,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6106,10 +6106,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252324</v>
+        <v>131252295</v>
       </c>
       <c r="B55" t="n">
-        <v>79007</v>
+        <v>79839</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6117,34 +6117,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431015</v>
+        <v>431735</v>
       </c>
       <c r="R55" t="n">
-        <v>6779783</v>
+        <v>6780060</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6185,6 +6188,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6203,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252295</v>
+        <v>131252324</v>
       </c>
       <c r="B56" t="n">
-        <v>79839</v>
+        <v>79007</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6214,37 +6218,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431735</v>
+        <v>431015</v>
       </c>
       <c r="R56" t="n">
-        <v>6780060</v>
+        <v>6779783</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,7 +6286,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252312</v>
+        <v>131252326</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>79007</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,31 +6315,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6347,10 +6342,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431640</v>
+        <v>431339</v>
       </c>
       <c r="R57" t="n">
-        <v>6780016</v>
+        <v>6779765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6391,6 +6386,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6409,7 +6405,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131252320</v>
+        <v>131252312</v>
       </c>
       <c r="B58" t="n">
         <v>57884</v>
@@ -6452,10 +6448,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431254</v>
+        <v>431640</v>
       </c>
       <c r="R58" t="n">
-        <v>6779775</v>
+        <v>6780016</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6708,10 +6704,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131252326</v>
+        <v>131252320</v>
       </c>
       <c r="B61" t="n">
-        <v>79007</v>
+        <v>57884</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6719,26 +6715,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6746,10 +6747,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431339</v>
+        <v>431254</v>
       </c>
       <c r="R61" t="n">
-        <v>6779765</v>
+        <v>6779775</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6790,7 +6791,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131252385</v>
+        <v>131252301</v>
       </c>
       <c r="B62" t="n">
-        <v>79249</v>
+        <v>58046</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,34 +6820,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431690</v>
+        <v>431747</v>
       </c>
       <c r="R62" t="n">
-        <v>6780037</v>
+        <v>6780081</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,7 +6914,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131252398</v>
+        <v>131252385</v>
       </c>
       <c r="B63" t="n">
         <v>79249</v>
@@ -6941,10 +6949,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431252</v>
+        <v>431690</v>
       </c>
       <c r="R63" t="n">
-        <v>6779759</v>
+        <v>6780037</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7003,10 +7011,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131252301</v>
+        <v>131252398</v>
       </c>
       <c r="B64" t="n">
-        <v>58046</v>
+        <v>79249</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7014,42 +7022,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431747</v>
+        <v>431252</v>
       </c>
       <c r="R64" t="n">
-        <v>6780081</v>
+        <v>6779759</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7627,7 +7627,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131252374</v>
+        <v>131252389</v>
       </c>
       <c r="B70" t="n">
         <v>79249</v>
@@ -7662,10 +7662,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431087</v>
+        <v>431389</v>
       </c>
       <c r="R70" t="n">
-        <v>6779811</v>
+        <v>6779928</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131252389</v>
+        <v>131252407</v>
       </c>
       <c r="B71" t="n">
         <v>79249</v>
@@ -7753,16 +7753,19 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431389</v>
+        <v>430942</v>
       </c>
       <c r="R71" t="n">
-        <v>6779928</v>
+        <v>6779693</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7803,6 +7806,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7821,37 +7825,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131252407</v>
+        <v>131252333</v>
       </c>
       <c r="B72" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7859,10 +7869,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430942</v>
+        <v>431385</v>
       </c>
       <c r="R72" t="n">
-        <v>6779693</v>
+        <v>6779961</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7922,10 +7932,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131252375</v>
+        <v>131252314</v>
       </c>
       <c r="B73" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7933,34 +7943,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431294</v>
+        <v>431448</v>
       </c>
       <c r="R73" t="n">
-        <v>6779898</v>
+        <v>6779825</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,10 +8037,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131252314</v>
+        <v>131252374</v>
       </c>
       <c r="B74" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8030,42 +8048,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431448</v>
+        <v>431087</v>
       </c>
       <c r="R74" t="n">
-        <v>6779825</v>
+        <v>6779811</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8124,54 +8134,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252333</v>
+        <v>131252375</v>
       </c>
       <c r="B75" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431385</v>
+        <v>431294</v>
       </c>
       <c r="R75" t="n">
-        <v>6779961</v>
+        <v>6779898</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,7 +8213,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8859,10 +8859,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131252383</v>
+        <v>131252315</v>
       </c>
       <c r="B82" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8870,34 +8870,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431745</v>
+        <v>431370</v>
       </c>
       <c r="R82" t="n">
-        <v>6780081</v>
+        <v>6779803</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8956,7 +8964,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131252379</v>
+        <v>131252383</v>
       </c>
       <c r="B83" t="n">
         <v>79249</v>
@@ -8991,10 +8999,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431606</v>
+        <v>431745</v>
       </c>
       <c r="R83" t="n">
-        <v>6780065</v>
+        <v>6780081</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9150,45 +9158,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131252380</v>
+        <v>131252335</v>
       </c>
       <c r="B85" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431673</v>
+        <v>431434</v>
       </c>
       <c r="R85" t="n">
-        <v>6780100</v>
+        <v>6779988</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9229,6 +9246,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9247,10 +9265,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131252315</v>
+        <v>131252379</v>
       </c>
       <c r="B86" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9258,42 +9276,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431370</v>
+        <v>431606</v>
       </c>
       <c r="R86" t="n">
-        <v>6779803</v>
+        <v>6780065</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9352,54 +9362,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131252335</v>
+        <v>131252380</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431434</v>
+        <v>431673</v>
       </c>
       <c r="R87" t="n">
-        <v>6779988</v>
+        <v>6780100</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9440,7 +9441,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9459,10 +9459,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131252323</v>
+        <v>131252304</v>
       </c>
       <c r="B88" t="n">
-        <v>57884</v>
+        <v>91838</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9470,31 +9470,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9502,10 +9497,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>431150</v>
+        <v>431613</v>
       </c>
       <c r="R88" t="n">
-        <v>6779694</v>
+        <v>6780015</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9546,6 +9541,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9564,10 +9560,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131252304</v>
+        <v>131252323</v>
       </c>
       <c r="B89" t="n">
-        <v>91838</v>
+        <v>57884</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9575,26 +9571,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9602,10 +9603,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>431613</v>
+        <v>431150</v>
       </c>
       <c r="R89" t="n">
-        <v>6780015</v>
+        <v>6779694</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9646,7 +9647,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9976,45 +9976,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131252293</v>
+        <v>131252300</v>
       </c>
       <c r="B93" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431669</v>
+        <v>431560</v>
       </c>
       <c r="R93" t="n">
-        <v>6780050</v>
+        <v>6779996</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10073,53 +10081,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131252300</v>
+        <v>131252293</v>
       </c>
       <c r="B94" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431560</v>
+        <v>431669</v>
       </c>
       <c r="R94" t="n">
-        <v>6779996</v>
+        <v>6780050</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10285,54 +10285,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131252409</v>
+        <v>131252382</v>
       </c>
       <c r="B96" t="n">
-        <v>5177</v>
+        <v>79249</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431446</v>
+        <v>431806</v>
       </c>
       <c r="R96" t="n">
-        <v>6779877</v>
+        <v>6780050</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10373,7 +10364,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10392,10 +10382,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131252382</v>
+        <v>131252305</v>
       </c>
       <c r="B97" t="n">
-        <v>79249</v>
+        <v>91838</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10403,34 +10393,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431806</v>
+        <v>431438</v>
       </c>
       <c r="R97" t="n">
-        <v>6780050</v>
+        <v>6779872</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10471,6 +10464,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10489,7 +10483,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131252378</v>
+        <v>131252388</v>
       </c>
       <c r="B98" t="n">
         <v>79249</v>
@@ -10524,10 +10518,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431561</v>
+        <v>431442</v>
       </c>
       <c r="R98" t="n">
-        <v>6780045</v>
+        <v>6779937</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10586,7 +10580,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131252388</v>
+        <v>131252378</v>
       </c>
       <c r="B99" t="n">
         <v>79249</v>
@@ -10621,10 +10615,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431442</v>
+        <v>431561</v>
       </c>
       <c r="R99" t="n">
-        <v>6779937</v>
+        <v>6780045</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10683,37 +10677,43 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131252305</v>
+        <v>131252409</v>
       </c>
       <c r="B100" t="n">
-        <v>91838</v>
+        <v>5177</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431438</v>
+        <v>431446</v>
       </c>
       <c r="R100" t="n">
-        <v>6779872</v>
+        <v>6779877</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131252377</v>
+        <v>131252370</v>
       </c>
       <c r="B2" t="n">
         <v>79249</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>431422</v>
+        <v>430909</v>
       </c>
       <c r="R2" t="n">
-        <v>6779979</v>
+        <v>6779703</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131252402</v>
+        <v>131252377</v>
       </c>
       <c r="B3" t="n">
         <v>79249</v>
@@ -801,19 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431075</v>
+        <v>431422</v>
       </c>
       <c r="R3" t="n">
-        <v>6779646</v>
+        <v>6779979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131252359</v>
+        <v>131252402</v>
       </c>
       <c r="B4" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,34 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431017</v>
+        <v>431075</v>
       </c>
       <c r="R4" t="n">
-        <v>6779783</v>
+        <v>6779646</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131252408</v>
+        <v>131252359</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430924</v>
+        <v>431017</v>
       </c>
       <c r="R5" t="n">
-        <v>6779690</v>
+        <v>6779783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131252370</v>
+        <v>131252408</v>
       </c>
       <c r="B6" t="n">
         <v>79249</v>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430909</v>
+        <v>430924</v>
       </c>
       <c r="R6" t="n">
-        <v>6779703</v>
+        <v>6779690</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1477,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131252294</v>
+        <v>131252400</v>
       </c>
       <c r="B10" t="n">
-        <v>79868</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431192</v>
+        <v>431231</v>
       </c>
       <c r="R10" t="n">
-        <v>6779695</v>
+        <v>6779719</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1574,54 +1574,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131252343</v>
+        <v>131252294</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431557</v>
+        <v>431192</v>
       </c>
       <c r="R11" t="n">
-        <v>6779992</v>
+        <v>6779695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,7 +1653,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1681,7 +1671,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131252344</v>
+        <v>131252343</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1715,7 +1705,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1725,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431546</v>
+        <v>431557</v>
       </c>
       <c r="R12" t="n">
-        <v>6779986</v>
+        <v>6779992</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,7 +1778,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131252358</v>
+        <v>131252344</v>
       </c>
       <c r="B13" t="n">
         <v>8451</v>
@@ -1822,7 +1812,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1832,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431077</v>
+        <v>431546</v>
       </c>
       <c r="R13" t="n">
-        <v>6779648</v>
+        <v>6779986</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1895,45 +1885,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131252400</v>
+        <v>131252358</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431231</v>
+        <v>431077</v>
       </c>
       <c r="R14" t="n">
-        <v>6779719</v>
+        <v>6779648</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,6 +1973,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131252390</v>
+        <v>131252393</v>
       </c>
       <c r="B16" t="n">
         <v>79249</v>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431416</v>
+        <v>431431</v>
       </c>
       <c r="R16" t="n">
-        <v>6779884</v>
+        <v>6779803</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,54 +2194,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131252413</v>
+        <v>131252390</v>
       </c>
       <c r="B17" t="n">
-        <v>8440</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431288</v>
+        <v>431416</v>
       </c>
       <c r="R17" t="n">
-        <v>6779800</v>
+        <v>6779884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,7 +2273,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2301,10 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131252342</v>
+        <v>131252413</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>8440</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2312,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2345,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431644</v>
+        <v>431288</v>
       </c>
       <c r="R18" t="n">
-        <v>6780041</v>
+        <v>6779800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,7 +2398,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131252334</v>
+        <v>131252342</v>
       </c>
       <c r="B19" t="n">
         <v>8451</v>
@@ -2452,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431411</v>
+        <v>431644</v>
       </c>
       <c r="R19" t="n">
-        <v>6779968</v>
+        <v>6780041</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,7 +2505,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131252350</v>
+        <v>131252334</v>
       </c>
       <c r="B20" t="n">
         <v>8451</v>
@@ -2559,10 +2549,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431430</v>
+        <v>431411</v>
       </c>
       <c r="R20" t="n">
-        <v>6779818</v>
+        <v>6779968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,45 +2612,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131252393</v>
+        <v>131252350</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431431</v>
+        <v>431430</v>
       </c>
       <c r="R21" t="n">
-        <v>6779803</v>
+        <v>6779818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2701,6 +2700,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131252371</v>
+        <v>131252396</v>
       </c>
       <c r="B22" t="n">
         <v>79249</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>430998</v>
+        <v>431284</v>
       </c>
       <c r="R22" t="n">
-        <v>6779729</v>
+        <v>6779794</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131252391</v>
+        <v>131252392</v>
       </c>
       <c r="B23" t="n">
         <v>79249</v>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431447</v>
+        <v>431477</v>
       </c>
       <c r="R23" t="n">
-        <v>6779876</v>
+        <v>6779852</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131252381</v>
+        <v>131252386</v>
       </c>
       <c r="B24" t="n">
         <v>79249</v>
@@ -2942,19 +2942,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431806</v>
+        <v>431659</v>
       </c>
       <c r="R24" t="n">
-        <v>6780109</v>
+        <v>6780052</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2995,7 +2992,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3014,7 +3010,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131252405</v>
+        <v>131252371</v>
       </c>
       <c r="B25" t="n">
         <v>79249</v>
@@ -3049,10 +3045,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430989</v>
+        <v>430998</v>
       </c>
       <c r="R25" t="n">
-        <v>6779656</v>
+        <v>6779729</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3085,11 +3081,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3116,10 +3107,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131252321</v>
+        <v>131252391</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3127,42 +3118,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431232</v>
+        <v>431447</v>
       </c>
       <c r="R26" t="n">
-        <v>6779756</v>
+        <v>6779876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3221,7 +3204,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131252396</v>
+        <v>131252381</v>
       </c>
       <c r="B27" t="n">
         <v>79249</v>
@@ -3250,16 +3233,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431284</v>
+        <v>431806</v>
       </c>
       <c r="R27" t="n">
-        <v>6779794</v>
+        <v>6780109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3300,6 +3286,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3318,7 +3305,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131252392</v>
+        <v>131252405</v>
       </c>
       <c r="B28" t="n">
         <v>79249</v>
@@ -3353,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431477</v>
+        <v>430989</v>
       </c>
       <c r="R28" t="n">
-        <v>6779852</v>
+        <v>6779656</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3389,6 +3376,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3415,10 +3407,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131252386</v>
+        <v>131252321</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,34 +3418,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431659</v>
+        <v>431232</v>
       </c>
       <c r="R29" t="n">
-        <v>6780052</v>
+        <v>6779756</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3724,54 +3724,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131252346</v>
+        <v>131252403</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431434</v>
+        <v>431055</v>
       </c>
       <c r="R32" t="n">
-        <v>6779875</v>
+        <v>6779612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,13 +3797,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3831,54 +3826,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131252414</v>
+        <v>131252384</v>
       </c>
       <c r="B33" t="n">
-        <v>8440</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431245</v>
+        <v>431710</v>
       </c>
       <c r="R33" t="n">
-        <v>6779803</v>
+        <v>6780009</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3913,13 +3899,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3938,41 +3928,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131252357</v>
+        <v>131252316</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3982,10 +3971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431074</v>
+        <v>431357</v>
       </c>
       <c r="R34" t="n">
-        <v>6779685</v>
+        <v>6779763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,7 +4015,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4045,10 +4033,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131252403</v>
+        <v>131252325</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,34 +4044,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431055</v>
+        <v>431743</v>
       </c>
       <c r="R35" t="n">
-        <v>6779612</v>
+        <v>6780091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4118,17 +4109,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4147,45 +4134,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131252384</v>
+        <v>131252346</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431710</v>
+        <v>431434</v>
       </c>
       <c r="R36" t="n">
-        <v>6780009</v>
+        <v>6779875</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,17 +4216,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4249,37 +4241,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131252325</v>
+        <v>131252414</v>
       </c>
       <c r="B37" t="n">
-        <v>79007</v>
+        <v>8440</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4287,10 +4285,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431743</v>
+        <v>431245</v>
       </c>
       <c r="R37" t="n">
-        <v>6780091</v>
+        <v>6779803</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,40 +4348,41 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131252316</v>
+        <v>131252357</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4393,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431357</v>
+        <v>431074</v>
       </c>
       <c r="R38" t="n">
-        <v>6779763</v>
+        <v>6779685</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4437,6 +4436,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131252373</v>
+        <v>131252311</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4466,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431077</v>
+        <v>431487</v>
       </c>
       <c r="R39" t="n">
-        <v>6779777</v>
+        <v>6779989</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,45 +4560,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131252372</v>
+        <v>131252339</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431053</v>
+        <v>431754</v>
       </c>
       <c r="R40" t="n">
-        <v>6779790</v>
+        <v>6780143</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4631,6 +4648,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4649,45 +4667,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131252387</v>
+        <v>131252341</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431622</v>
+        <v>431684</v>
       </c>
       <c r="R41" t="n">
-        <v>6780004</v>
+        <v>6780041</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,6 +4755,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4746,10 +4774,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131252311</v>
+        <v>131252373</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4757,42 +4785,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431487</v>
+        <v>431077</v>
       </c>
       <c r="R42" t="n">
-        <v>6779989</v>
+        <v>6779777</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4851,54 +4871,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131252339</v>
+        <v>131252372</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431754</v>
+        <v>431053</v>
       </c>
       <c r="R43" t="n">
-        <v>6780143</v>
+        <v>6779790</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4939,7 +4950,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4958,54 +4968,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131252341</v>
+        <v>131252387</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431684</v>
+        <v>431622</v>
       </c>
       <c r="R44" t="n">
-        <v>6780041</v>
+        <v>6780004</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5046,7 +5047,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5162,40 +5162,41 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131252313</v>
+        <v>131252340</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5205,10 +5206,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431580</v>
+        <v>431705</v>
       </c>
       <c r="R46" t="n">
-        <v>6779970</v>
+        <v>6779985</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,6 +5250,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5267,7 +5269,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131252340</v>
+        <v>131252336</v>
       </c>
       <c r="B47" t="n">
         <v>8451</v>
@@ -5301,7 +5303,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5311,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431705</v>
+        <v>431610</v>
       </c>
       <c r="R47" t="n">
-        <v>6779985</v>
+        <v>6780067</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5374,41 +5376,40 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131252336</v>
+        <v>131252313</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5418,10 +5419,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431610</v>
+        <v>431580</v>
       </c>
       <c r="R48" t="n">
-        <v>6780067</v>
+        <v>6779970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5462,7 +5463,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131252401</v>
+        <v>131252295</v>
       </c>
       <c r="B49" t="n">
-        <v>79249</v>
+        <v>79839</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,34 +5492,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431082</v>
+        <v>431735</v>
       </c>
       <c r="R49" t="n">
-        <v>6779651</v>
+        <v>6780060</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5554,17 +5557,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5583,10 +5582,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252395</v>
+        <v>131252324</v>
       </c>
       <c r="B50" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5594,21 +5593,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5618,10 +5617,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431310</v>
+        <v>431015</v>
       </c>
       <c r="R50" t="n">
-        <v>6779809</v>
+        <v>6779783</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5680,10 +5679,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252322</v>
+        <v>131252401</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5691,42 +5690,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431214</v>
+        <v>431082</v>
       </c>
       <c r="R51" t="n">
-        <v>6779702</v>
+        <v>6779651</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5759,6 +5750,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5785,54 +5781,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252337</v>
+        <v>131252395</v>
       </c>
       <c r="B52" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431622</v>
+        <v>431310</v>
       </c>
       <c r="R52" t="n">
-        <v>6780061</v>
+        <v>6779809</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5873,7 +5860,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5892,41 +5878,40 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252352</v>
+        <v>131252322</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5936,10 +5921,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431374</v>
+        <v>431214</v>
       </c>
       <c r="R53" t="n">
-        <v>6779783</v>
+        <v>6779702</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5980,7 +5965,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5999,7 +5983,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252355</v>
+        <v>131252337</v>
       </c>
       <c r="B54" t="n">
         <v>8451</v>
@@ -6043,10 +6027,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431356</v>
+        <v>431622</v>
       </c>
       <c r="R54" t="n">
-        <v>6779743</v>
+        <v>6780061</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,37 +6090,43 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252295</v>
+        <v>131252352</v>
       </c>
       <c r="B55" t="n">
-        <v>79839</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6144,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431735</v>
+        <v>431374</v>
       </c>
       <c r="R55" t="n">
-        <v>6780060</v>
+        <v>6779783</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6207,45 +6197,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252324</v>
+        <v>131252355</v>
       </c>
       <c r="B56" t="n">
-        <v>79007</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431015</v>
+        <v>431356</v>
       </c>
       <c r="R56" t="n">
-        <v>6779783</v>
+        <v>6779743</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6286,6 +6285,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252326</v>
+        <v>131252312</v>
       </c>
       <c r="B57" t="n">
-        <v>79007</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,26 +6315,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6342,10 +6347,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431339</v>
+        <v>431640</v>
       </c>
       <c r="R57" t="n">
-        <v>6779765</v>
+        <v>6780016</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6386,7 +6391,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6405,7 +6409,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131252312</v>
+        <v>131252320</v>
       </c>
       <c r="B58" t="n">
         <v>57884</v>
@@ -6448,10 +6452,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431640</v>
+        <v>431254</v>
       </c>
       <c r="R58" t="n">
-        <v>6780016</v>
+        <v>6779775</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6510,10 +6514,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131252376</v>
+        <v>131252326</v>
       </c>
       <c r="B59" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6521,34 +6525,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431316</v>
+        <v>431339</v>
       </c>
       <c r="R59" t="n">
-        <v>6779925</v>
+        <v>6779765</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6589,6 +6596,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6607,7 +6615,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131252397</v>
+        <v>131252376</v>
       </c>
       <c r="B60" t="n">
         <v>79249</v>
@@ -6642,10 +6650,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431280</v>
+        <v>431316</v>
       </c>
       <c r="R60" t="n">
-        <v>6779815</v>
+        <v>6779925</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6704,10 +6712,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131252320</v>
+        <v>131252397</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6715,42 +6723,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431254</v>
+        <v>431280</v>
       </c>
       <c r="R61" t="n">
-        <v>6779775</v>
+        <v>6779815</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7108,10 +7108,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131252360</v>
+        <v>131252302</v>
       </c>
       <c r="B65" t="n">
-        <v>79006</v>
+        <v>91838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7119,34 +7119,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430970</v>
+        <v>431364</v>
       </c>
       <c r="R65" t="n">
-        <v>6779700</v>
+        <v>6779943</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7187,6 +7190,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7205,10 +7209,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131252302</v>
+        <v>131252360</v>
       </c>
       <c r="B66" t="n">
-        <v>91838</v>
+        <v>79006</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7216,37 +7220,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431364</v>
+        <v>430970</v>
       </c>
       <c r="R66" t="n">
-        <v>6779943</v>
+        <v>6779700</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7287,7 +7288,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131252389</v>
+        <v>131252314</v>
       </c>
       <c r="B70" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7638,34 +7638,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431389</v>
+        <v>431448</v>
       </c>
       <c r="R70" t="n">
-        <v>6779928</v>
+        <v>6779825</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7724,7 +7732,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131252407</v>
+        <v>131252374</v>
       </c>
       <c r="B71" t="n">
         <v>79249</v>
@@ -7753,19 +7761,16 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430942</v>
+        <v>431087</v>
       </c>
       <c r="R71" t="n">
-        <v>6779693</v>
+        <v>6779811</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7806,7 +7811,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7825,54 +7829,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131252333</v>
+        <v>131252389</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431385</v>
+        <v>431389</v>
       </c>
       <c r="R72" t="n">
-        <v>6779961</v>
+        <v>6779928</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7913,7 +7908,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7932,10 +7926,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131252314</v>
+        <v>131252407</v>
       </c>
       <c r="B73" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,31 +7937,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7975,10 +7964,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431448</v>
+        <v>430942</v>
       </c>
       <c r="R73" t="n">
-        <v>6779825</v>
+        <v>6779693</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,6 +8008,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8037,7 +8027,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131252374</v>
+        <v>131252375</v>
       </c>
       <c r="B74" t="n">
         <v>79249</v>
@@ -8072,10 +8062,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431087</v>
+        <v>431294</v>
       </c>
       <c r="R74" t="n">
-        <v>6779811</v>
+        <v>6779898</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8134,45 +8124,54 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252375</v>
+        <v>131252333</v>
       </c>
       <c r="B75" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431294</v>
+        <v>431385</v>
       </c>
       <c r="R75" t="n">
-        <v>6779898</v>
+        <v>6779961</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,6 +8212,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8231,45 +8231,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131252406</v>
+        <v>131252347</v>
       </c>
       <c r="B76" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430975</v>
+        <v>431446</v>
       </c>
       <c r="R76" t="n">
-        <v>6779698</v>
+        <v>6779877</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8310,6 +8319,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8328,10 +8338,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131252306</v>
+        <v>131252406</v>
       </c>
       <c r="B77" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8339,42 +8349,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430985</v>
+        <v>430975</v>
       </c>
       <c r="R77" t="n">
-        <v>6779728</v>
+        <v>6779698</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8433,7 +8435,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252308</v>
+        <v>131252306</v>
       </c>
       <c r="B78" t="n">
         <v>57884</v>
@@ -8476,10 +8478,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431243</v>
+        <v>430985</v>
       </c>
       <c r="R78" t="n">
-        <v>6779888</v>
+        <v>6779728</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8538,41 +8540,40 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131252347</v>
+        <v>131252308</v>
       </c>
       <c r="B79" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8582,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431446</v>
+        <v>431243</v>
       </c>
       <c r="R79" t="n">
-        <v>6779877</v>
+        <v>6779888</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8626,7 +8627,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8859,10 +8859,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131252315</v>
+        <v>131252380</v>
       </c>
       <c r="B82" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8870,42 +8870,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431370</v>
+        <v>431673</v>
       </c>
       <c r="R82" t="n">
-        <v>6779803</v>
+        <v>6780100</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8964,10 +8956,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131252383</v>
+        <v>131252315</v>
       </c>
       <c r="B83" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8975,34 +8967,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431745</v>
+        <v>431370</v>
       </c>
       <c r="R83" t="n">
-        <v>6780081</v>
+        <v>6779803</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9061,7 +9061,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131252404</v>
+        <v>131252383</v>
       </c>
       <c r="B84" t="n">
         <v>79249</v>
@@ -9096,10 +9096,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431024</v>
+        <v>431745</v>
       </c>
       <c r="R84" t="n">
-        <v>6779638</v>
+        <v>6780081</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9158,54 +9158,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131252335</v>
+        <v>131252379</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431434</v>
+        <v>431606</v>
       </c>
       <c r="R85" t="n">
-        <v>6779988</v>
+        <v>6780065</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9246,7 +9237,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9265,7 +9255,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131252379</v>
+        <v>131252404</v>
       </c>
       <c r="B86" t="n">
         <v>79249</v>
@@ -9300,10 +9290,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431606</v>
+        <v>431024</v>
       </c>
       <c r="R86" t="n">
-        <v>6780065</v>
+        <v>6779638</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9362,45 +9352,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131252380</v>
+        <v>131252335</v>
       </c>
       <c r="B87" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>431673</v>
+        <v>431434</v>
       </c>
       <c r="R87" t="n">
-        <v>6780100</v>
+        <v>6779988</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9441,6 +9440,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9665,45 +9665,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131252394</v>
+        <v>131252331</v>
       </c>
       <c r="B90" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431327</v>
+        <v>431291</v>
       </c>
       <c r="R90" t="n">
-        <v>6779796</v>
+        <v>6779892</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9744,6 +9753,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9762,7 +9772,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131252331</v>
+        <v>131252330</v>
       </c>
       <c r="B91" t="n">
         <v>8451</v>
@@ -9806,10 +9816,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431291</v>
+        <v>431075</v>
       </c>
       <c r="R91" t="n">
-        <v>6779892</v>
+        <v>6779775</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9869,54 +9879,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131252330</v>
+        <v>131252394</v>
       </c>
       <c r="B92" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431075</v>
+        <v>431327</v>
       </c>
       <c r="R92" t="n">
-        <v>6779775</v>
+        <v>6779796</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9957,7 +9958,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9976,53 +9976,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131252300</v>
+        <v>131252293</v>
       </c>
       <c r="B93" t="n">
-        <v>57076</v>
+        <v>79868</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431560</v>
+        <v>431669</v>
       </c>
       <c r="R93" t="n">
-        <v>6779996</v>
+        <v>6780050</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10081,45 +10073,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131252293</v>
+        <v>131252300</v>
       </c>
       <c r="B94" t="n">
-        <v>79868</v>
+        <v>57076</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431669</v>
+        <v>431560</v>
       </c>
       <c r="R94" t="n">
-        <v>6780050</v>
+        <v>6779996</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131252382</v>
+        <v>131252305</v>
       </c>
       <c r="B96" t="n">
-        <v>79249</v>
+        <v>91838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10296,34 +10296,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431806</v>
+        <v>431438</v>
       </c>
       <c r="R96" t="n">
-        <v>6780050</v>
+        <v>6779872</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10364,6 +10367,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10382,10 +10386,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131252305</v>
+        <v>131252382</v>
       </c>
       <c r="B97" t="n">
-        <v>91838</v>
+        <v>79249</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10393,37 +10397,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431438</v>
+        <v>431806</v>
       </c>
       <c r="R97" t="n">
-        <v>6779872</v>
+        <v>6780050</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10464,7 +10465,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10483,7 +10483,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131252388</v>
+        <v>131252378</v>
       </c>
       <c r="B98" t="n">
         <v>79249</v>
@@ -10518,10 +10518,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431442</v>
+        <v>431561</v>
       </c>
       <c r="R98" t="n">
-        <v>6779937</v>
+        <v>6780045</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131252378</v>
+        <v>131252388</v>
       </c>
       <c r="B99" t="n">
         <v>79249</v>
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431561</v>
+        <v>431442</v>
       </c>
       <c r="R99" t="n">
-        <v>6780045</v>
+        <v>6779937</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131252370</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131252377</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131252402</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131252359</v>
+        <v>131252408</v>
       </c>
       <c r="B5" t="n">
-        <v>79006</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431017</v>
+        <v>430924</v>
       </c>
       <c r="R5" t="n">
-        <v>6779783</v>
+        <v>6779690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131252408</v>
+        <v>131252359</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>430924</v>
+        <v>431017</v>
       </c>
       <c r="R6" t="n">
-        <v>6779690</v>
+        <v>6779783</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,7 @@
         <v>131252303</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>131252319</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131252400</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>131252294</v>
       </c>
       <c r="B11" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131252317</v>
+        <v>131252393</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,42 +2003,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431356</v>
+        <v>431431</v>
       </c>
       <c r="R15" t="n">
-        <v>6779743</v>
+        <v>6779803</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131252393</v>
+        <v>131252390</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431431</v>
+        <v>431416</v>
       </c>
       <c r="R16" t="n">
-        <v>6779803</v>
+        <v>6779884</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131252390</v>
+        <v>131252317</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,34 +2197,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431416</v>
+        <v>431356</v>
       </c>
       <c r="R17" t="n">
-        <v>6779884</v>
+        <v>6779743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2722,7 +2722,7 @@
         <v>131252396</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>131252392</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131252386</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>131252371</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>131252391</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>131252381</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>131252405</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>131252321</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>131252309</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,45 +3724,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131252403</v>
+        <v>131252346</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431055</v>
+        <v>431434</v>
       </c>
       <c r="R32" t="n">
-        <v>6779612</v>
+        <v>6779875</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3797,17 +3806,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3826,45 +3831,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131252384</v>
+        <v>131252414</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>8440</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431710</v>
+        <v>431245</v>
       </c>
       <c r="R33" t="n">
-        <v>6780009</v>
+        <v>6779803</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3899,17 +3913,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3928,40 +3938,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131252316</v>
+        <v>131252357</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3971,10 +3982,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431357</v>
+        <v>431074</v>
       </c>
       <c r="R34" t="n">
-        <v>6779763</v>
+        <v>6779685</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4015,6 +4026,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4033,10 +4045,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131252325</v>
+        <v>131252403</v>
       </c>
       <c r="B35" t="n">
-        <v>79007</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,37 +4056,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431743</v>
+        <v>431055</v>
       </c>
       <c r="R35" t="n">
-        <v>6780091</v>
+        <v>6779612</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4109,13 +4118,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4134,54 +4147,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131252346</v>
+        <v>131252384</v>
       </c>
       <c r="B36" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431434</v>
+        <v>431710</v>
       </c>
       <c r="R36" t="n">
-        <v>6779875</v>
+        <v>6780009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,13 +4220,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4241,41 +4249,40 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131252414</v>
+        <v>131252316</v>
       </c>
       <c r="B37" t="n">
-        <v>8440</v>
+        <v>57885</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4285,10 +4292,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431245</v>
+        <v>431357</v>
       </c>
       <c r="R37" t="n">
-        <v>6779803</v>
+        <v>6779763</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4329,7 +4336,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4348,43 +4354,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131252357</v>
+        <v>131252325</v>
       </c>
       <c r="B38" t="n">
-        <v>8451</v>
+        <v>79008</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431074</v>
+        <v>431743</v>
       </c>
       <c r="R38" t="n">
-        <v>6779685</v>
+        <v>6780091</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,40 +4455,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131252311</v>
+        <v>131252339</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4498,10 +4499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431487</v>
+        <v>431754</v>
       </c>
       <c r="R39" t="n">
-        <v>6779989</v>
+        <v>6780143</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4542,6 +4543,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4560,7 +4562,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131252339</v>
+        <v>131252341</v>
       </c>
       <c r="B40" t="n">
         <v>8451</v>
@@ -4604,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431754</v>
+        <v>431684</v>
       </c>
       <c r="R40" t="n">
-        <v>6780143</v>
+        <v>6780041</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,54 +4669,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131252341</v>
+        <v>131252373</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431684</v>
+        <v>431077</v>
       </c>
       <c r="R41" t="n">
-        <v>6780041</v>
+        <v>6779777</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,7 +4748,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4774,10 +4766,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131252373</v>
+        <v>131252372</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4809,10 +4801,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431077</v>
+        <v>431053</v>
       </c>
       <c r="R42" t="n">
-        <v>6779777</v>
+        <v>6779790</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,10 +4863,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131252372</v>
+        <v>131252387</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4906,10 +4898,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431053</v>
+        <v>431622</v>
       </c>
       <c r="R43" t="n">
-        <v>6779790</v>
+        <v>6780004</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4968,10 +4960,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131252387</v>
+        <v>131252311</v>
       </c>
       <c r="B44" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4979,34 +4971,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431622</v>
+        <v>431487</v>
       </c>
       <c r="R44" t="n">
-        <v>6780004</v>
+        <v>6779989</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131252399</v>
+        <v>131252313</v>
       </c>
       <c r="B45" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,34 +5076,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431257</v>
+        <v>431580</v>
       </c>
       <c r="R45" t="n">
-        <v>6779698</v>
+        <v>6779970</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5162,54 +5170,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131252340</v>
+        <v>131252399</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431705</v>
+        <v>431257</v>
       </c>
       <c r="R46" t="n">
-        <v>6779985</v>
+        <v>6779698</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,7 +5249,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5269,7 +5267,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131252336</v>
+        <v>131252340</v>
       </c>
       <c r="B47" t="n">
         <v>8451</v>
@@ -5303,7 +5301,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5313,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431610</v>
+        <v>431705</v>
       </c>
       <c r="R47" t="n">
-        <v>6780067</v>
+        <v>6779985</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,40 +5374,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131252313</v>
+        <v>131252336</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5419,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431580</v>
+        <v>431610</v>
       </c>
       <c r="R48" t="n">
-        <v>6779970</v>
+        <v>6780067</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,6 +5462,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>131252295</v>
       </c>
       <c r="B49" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5582,10 +5582,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252324</v>
+        <v>131252401</v>
       </c>
       <c r="B50" t="n">
-        <v>79007</v>
+        <v>79250</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5593,21 +5593,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431015</v>
+        <v>431082</v>
       </c>
       <c r="R50" t="n">
-        <v>6779783</v>
+        <v>6779651</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5653,6 +5653,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5679,10 +5684,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252401</v>
+        <v>131252395</v>
       </c>
       <c r="B51" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5714,10 +5719,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431082</v>
+        <v>431310</v>
       </c>
       <c r="R51" t="n">
-        <v>6779651</v>
+        <v>6779809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5750,11 +5755,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5781,10 +5781,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252395</v>
+        <v>131252322</v>
       </c>
       <c r="B52" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5792,34 +5792,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431310</v>
+        <v>431214</v>
       </c>
       <c r="R52" t="n">
-        <v>6779809</v>
+        <v>6779702</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5878,40 +5886,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252322</v>
+        <v>131252337</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5921,10 +5930,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431214</v>
+        <v>431622</v>
       </c>
       <c r="R53" t="n">
-        <v>6779702</v>
+        <v>6780061</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5965,6 +5974,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5983,7 +5993,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252337</v>
+        <v>131252352</v>
       </c>
       <c r="B54" t="n">
         <v>8451</v>
@@ -6017,7 +6027,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6027,10 +6037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431622</v>
+        <v>431374</v>
       </c>
       <c r="R54" t="n">
-        <v>6780061</v>
+        <v>6779783</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,7 +6100,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252352</v>
+        <v>131252355</v>
       </c>
       <c r="B55" t="n">
         <v>8451</v>
@@ -6124,7 +6134,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6134,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431374</v>
+        <v>431356</v>
       </c>
       <c r="R55" t="n">
-        <v>6779783</v>
+        <v>6779743</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6197,54 +6207,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252355</v>
+        <v>131252324</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431356</v>
+        <v>431015</v>
       </c>
       <c r="R56" t="n">
-        <v>6779743</v>
+        <v>6779783</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,7 +6286,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252312</v>
+        <v>131252376</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,42 +6315,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431640</v>
+        <v>431316</v>
       </c>
       <c r="R57" t="n">
-        <v>6780016</v>
+        <v>6779925</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6409,10 +6401,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131252320</v>
+        <v>131252397</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6420,42 +6412,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431254</v>
+        <v>431280</v>
       </c>
       <c r="R58" t="n">
-        <v>6779775</v>
+        <v>6779815</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,10 +6498,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131252326</v>
+        <v>131252312</v>
       </c>
       <c r="B59" t="n">
-        <v>79007</v>
+        <v>57885</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6525,26 +6509,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6552,10 +6541,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431339</v>
+        <v>431640</v>
       </c>
       <c r="R59" t="n">
-        <v>6779765</v>
+        <v>6780016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6596,7 +6585,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6615,10 +6603,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131252376</v>
+        <v>131252320</v>
       </c>
       <c r="B60" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6626,34 +6614,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431316</v>
+        <v>431254</v>
       </c>
       <c r="R60" t="n">
-        <v>6779925</v>
+        <v>6779775</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6712,10 +6708,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131252397</v>
+        <v>131252326</v>
       </c>
       <c r="B61" t="n">
-        <v>79249</v>
+        <v>79008</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6723,34 +6719,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431280</v>
+        <v>431339</v>
       </c>
       <c r="R61" t="n">
-        <v>6779815</v>
+        <v>6779765</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6791,6 +6790,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>131252301</v>
       </c>
       <c r="B62" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>131252385</v>
       </c>
       <c r="B63" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>131252398</v>
       </c>
       <c r="B64" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7108,37 +7108,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131252302</v>
+        <v>131252328</v>
       </c>
       <c r="B65" t="n">
-        <v>91838</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7146,10 +7152,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431364</v>
+        <v>431002</v>
       </c>
       <c r="R65" t="n">
-        <v>6779943</v>
+        <v>6779756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7209,45 +7215,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131252360</v>
+        <v>131252351</v>
       </c>
       <c r="B66" t="n">
-        <v>79006</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430970</v>
+        <v>431370</v>
       </c>
       <c r="R66" t="n">
-        <v>6779700</v>
+        <v>6779803</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7288,6 +7303,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7306,7 +7322,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131252328</v>
+        <v>131252354</v>
       </c>
       <c r="B67" t="n">
         <v>8451</v>
@@ -7340,7 +7356,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7350,10 +7366,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431002</v>
+        <v>431358</v>
       </c>
       <c r="R67" t="n">
-        <v>6779756</v>
+        <v>6779744</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7413,43 +7429,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131252351</v>
+        <v>131252302</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>91839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7457,10 +7467,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431370</v>
+        <v>431364</v>
       </c>
       <c r="R68" t="n">
-        <v>6779803</v>
+        <v>6779943</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7520,54 +7530,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131252354</v>
+        <v>131252360</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>79007</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431358</v>
+        <v>430970</v>
       </c>
       <c r="R69" t="n">
-        <v>6779744</v>
+        <v>6779700</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7608,7 +7609,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7627,40 +7627,41 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131252314</v>
+        <v>131252333</v>
       </c>
       <c r="B70" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7670,10 +7671,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431448</v>
+        <v>431385</v>
       </c>
       <c r="R70" t="n">
-        <v>6779825</v>
+        <v>6779961</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7714,6 +7715,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7735,7 +7737,7 @@
         <v>131252374</v>
       </c>
       <c r="B71" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7832,7 +7834,7 @@
         <v>131252389</v>
       </c>
       <c r="B72" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7929,7 +7931,7 @@
         <v>131252407</v>
       </c>
       <c r="B73" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8030,7 +8032,7 @@
         <v>131252375</v>
       </c>
       <c r="B74" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8124,41 +8126,40 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252333</v>
+        <v>131252314</v>
       </c>
       <c r="B75" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8168,10 +8169,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431385</v>
+        <v>431448</v>
       </c>
       <c r="R75" t="n">
-        <v>6779961</v>
+        <v>6779825</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,7 +8213,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8231,41 +8231,40 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131252347</v>
+        <v>131252306</v>
       </c>
       <c r="B76" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8275,10 +8274,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431446</v>
+        <v>430985</v>
       </c>
       <c r="R76" t="n">
-        <v>6779877</v>
+        <v>6779728</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8319,7 +8318,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8338,10 +8336,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131252406</v>
+        <v>131252308</v>
       </c>
       <c r="B77" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8349,34 +8347,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>430975</v>
+        <v>431243</v>
       </c>
       <c r="R77" t="n">
-        <v>6779698</v>
+        <v>6779888</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8435,10 +8441,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252306</v>
+        <v>131252406</v>
       </c>
       <c r="B78" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8446,42 +8452,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430985</v>
+        <v>430975</v>
       </c>
       <c r="R78" t="n">
-        <v>6779728</v>
+        <v>6779698</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8540,40 +8538,41 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131252308</v>
+        <v>131252347</v>
       </c>
       <c r="B79" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8583,10 +8582,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431243</v>
+        <v>431446</v>
       </c>
       <c r="R79" t="n">
-        <v>6779888</v>
+        <v>6779877</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8627,6 +8626,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8859,10 +8859,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131252380</v>
+        <v>131252383</v>
       </c>
       <c r="B82" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431673</v>
+        <v>431745</v>
       </c>
       <c r="R82" t="n">
-        <v>6780100</v>
+        <v>6780081</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8956,10 +8956,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131252315</v>
+        <v>131252379</v>
       </c>
       <c r="B83" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8967,42 +8967,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431370</v>
+        <v>431606</v>
       </c>
       <c r="R83" t="n">
-        <v>6779803</v>
+        <v>6780065</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9061,10 +9053,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131252383</v>
+        <v>131252404</v>
       </c>
       <c r="B84" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9096,10 +9088,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431745</v>
+        <v>431024</v>
       </c>
       <c r="R84" t="n">
-        <v>6780081</v>
+        <v>6779638</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9158,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131252379</v>
+        <v>131252380</v>
       </c>
       <c r="B85" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9193,10 +9185,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431606</v>
+        <v>431673</v>
       </c>
       <c r="R85" t="n">
-        <v>6780065</v>
+        <v>6780100</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9255,10 +9247,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131252404</v>
+        <v>131252315</v>
       </c>
       <c r="B86" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9266,34 +9258,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431024</v>
+        <v>431370</v>
       </c>
       <c r="R86" t="n">
-        <v>6779638</v>
+        <v>6779803</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9462,7 +9462,7 @@
         <v>131252304</v>
       </c>
       <c r="B88" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>131252323</v>
       </c>
       <c r="B89" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9665,54 +9665,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131252331</v>
+        <v>131252394</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431291</v>
+        <v>431327</v>
       </c>
       <c r="R90" t="n">
-        <v>6779892</v>
+        <v>6779796</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9753,7 +9744,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9772,7 +9762,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131252330</v>
+        <v>131252331</v>
       </c>
       <c r="B91" t="n">
         <v>8451</v>
@@ -9816,10 +9806,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431075</v>
+        <v>431291</v>
       </c>
       <c r="R91" t="n">
-        <v>6779775</v>
+        <v>6779892</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9879,45 +9869,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131252394</v>
+        <v>131252330</v>
       </c>
       <c r="B92" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431327</v>
+        <v>431075</v>
       </c>
       <c r="R92" t="n">
-        <v>6779796</v>
+        <v>6779775</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9958,6 +9957,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9979,7 +9979,7 @@
         <v>131252293</v>
       </c>
       <c r="B93" t="n">
-        <v>79868</v>
+        <v>79869</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10285,37 +10285,43 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131252305</v>
+        <v>131252409</v>
       </c>
       <c r="B96" t="n">
-        <v>91838</v>
+        <v>5177</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10323,10 +10329,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431438</v>
+        <v>431446</v>
       </c>
       <c r="R96" t="n">
-        <v>6779872</v>
+        <v>6779877</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10386,45 +10392,54 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131252382</v>
+        <v>131252353</v>
       </c>
       <c r="B97" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431806</v>
+        <v>431372</v>
       </c>
       <c r="R97" t="n">
-        <v>6780050</v>
+        <v>6779775</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10465,6 +10480,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10483,10 +10499,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131252378</v>
+        <v>131252382</v>
       </c>
       <c r="B98" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10518,10 +10534,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431561</v>
+        <v>431806</v>
       </c>
       <c r="R98" t="n">
-        <v>6780045</v>
+        <v>6780050</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10580,10 +10596,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131252388</v>
+        <v>131252378</v>
       </c>
       <c r="B99" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10615,10 +10631,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431442</v>
+        <v>431561</v>
       </c>
       <c r="R99" t="n">
-        <v>6779937</v>
+        <v>6780045</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10677,43 +10693,37 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131252409</v>
+        <v>131252305</v>
       </c>
       <c r="B100" t="n">
-        <v>5177</v>
+        <v>91839</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10721,10 +10731,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431446</v>
+        <v>431438</v>
       </c>
       <c r="R100" t="n">
-        <v>6779877</v>
+        <v>6779872</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10784,54 +10794,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131252353</v>
+        <v>131252388</v>
       </c>
       <c r="B101" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431372</v>
+        <v>431442</v>
       </c>
       <c r="R101" t="n">
-        <v>6779775</v>
+        <v>6779937</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10872,7 +10873,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131252370</v>
+        <v>131252377</v>
       </c>
       <c r="B2" t="n">
         <v>79250</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430909</v>
+        <v>431422</v>
       </c>
       <c r="R2" t="n">
-        <v>6779703</v>
+        <v>6779979</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131252377</v>
+        <v>131252402</v>
       </c>
       <c r="B3" t="n">
         <v>79250</v>
@@ -801,16 +801,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431422</v>
+        <v>431075</v>
       </c>
       <c r="R3" t="n">
-        <v>6779979</v>
+        <v>6779646</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,7 +873,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131252402</v>
+        <v>131252370</v>
       </c>
       <c r="B4" t="n">
         <v>79250</v>
@@ -898,19 +902,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>431075</v>
+        <v>430909</v>
       </c>
       <c r="R4" t="n">
-        <v>6779646</v>
+        <v>6779703</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131252408</v>
+        <v>131252359</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430924</v>
+        <v>431017</v>
       </c>
       <c r="R5" t="n">
-        <v>6779690</v>
+        <v>6779783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,10 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131252359</v>
+        <v>131252408</v>
       </c>
       <c r="B6" t="n">
-        <v>79007</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1078,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431017</v>
+        <v>430924</v>
       </c>
       <c r="R6" t="n">
-        <v>6779783</v>
+        <v>6779690</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131252386</v>
+        <v>131252371</v>
       </c>
       <c r="B24" t="n">
         <v>79250</v>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431659</v>
+        <v>430998</v>
       </c>
       <c r="R24" t="n">
-        <v>6780052</v>
+        <v>6779729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3010,7 +3010,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131252371</v>
+        <v>131252391</v>
       </c>
       <c r="B25" t="n">
         <v>79250</v>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430998</v>
+        <v>431447</v>
       </c>
       <c r="R25" t="n">
-        <v>6779729</v>
+        <v>6779876</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,7 +3107,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131252391</v>
+        <v>131252381</v>
       </c>
       <c r="B26" t="n">
         <v>79250</v>
@@ -3136,16 +3136,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431447</v>
+        <v>431806</v>
       </c>
       <c r="R26" t="n">
-        <v>6779876</v>
+        <v>6780109</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3186,6 +3189,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3204,7 +3208,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131252381</v>
+        <v>131252405</v>
       </c>
       <c r="B27" t="n">
         <v>79250</v>
@@ -3233,19 +3237,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431806</v>
+        <v>430989</v>
       </c>
       <c r="R27" t="n">
-        <v>6780109</v>
+        <v>6779656</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,13 +3281,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3305,7 +3310,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131252405</v>
+        <v>131252386</v>
       </c>
       <c r="B28" t="n">
         <v>79250</v>
@@ -3340,10 +3345,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>430989</v>
+        <v>431659</v>
       </c>
       <c r="R28" t="n">
-        <v>6779656</v>
+        <v>6780052</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3376,11 +3381,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4455,41 +4455,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131252339</v>
+        <v>131252311</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4499,10 +4498,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431754</v>
+        <v>431487</v>
       </c>
       <c r="R39" t="n">
-        <v>6780143</v>
+        <v>6779989</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4543,7 +4542,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4562,7 +4560,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131252341</v>
+        <v>131252339</v>
       </c>
       <c r="B40" t="n">
         <v>8451</v>
@@ -4606,10 +4604,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431684</v>
+        <v>431754</v>
       </c>
       <c r="R40" t="n">
-        <v>6780041</v>
+        <v>6780143</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4669,45 +4667,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131252373</v>
+        <v>131252341</v>
       </c>
       <c r="B41" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431077</v>
+        <v>431684</v>
       </c>
       <c r="R41" t="n">
-        <v>6779777</v>
+        <v>6780041</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4748,6 +4755,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4766,7 +4774,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131252372</v>
+        <v>131252373</v>
       </c>
       <c r="B42" t="n">
         <v>79250</v>
@@ -4801,10 +4809,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431053</v>
+        <v>431077</v>
       </c>
       <c r="R42" t="n">
-        <v>6779790</v>
+        <v>6779777</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,7 +4871,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131252387</v>
+        <v>131252372</v>
       </c>
       <c r="B43" t="n">
         <v>79250</v>
@@ -4898,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431622</v>
+        <v>431053</v>
       </c>
       <c r="R43" t="n">
-        <v>6780004</v>
+        <v>6779790</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4960,10 +4968,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131252311</v>
+        <v>131252387</v>
       </c>
       <c r="B44" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4971,42 +4979,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431487</v>
+        <v>431622</v>
       </c>
       <c r="R44" t="n">
-        <v>6779989</v>
+        <v>6780004</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131252313</v>
+        <v>131252399</v>
       </c>
       <c r="B45" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,42 +5076,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431580</v>
+        <v>431257</v>
       </c>
       <c r="R45" t="n">
-        <v>6779970</v>
+        <v>6779698</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5170,45 +5162,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131252399</v>
+        <v>131252340</v>
       </c>
       <c r="B46" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431257</v>
+        <v>431705</v>
       </c>
       <c r="R46" t="n">
-        <v>6779698</v>
+        <v>6779985</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,6 +5250,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5267,7 +5269,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131252340</v>
+        <v>131252336</v>
       </c>
       <c r="B47" t="n">
         <v>8451</v>
@@ -5301,7 +5303,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5311,10 +5313,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431705</v>
+        <v>431610</v>
       </c>
       <c r="R47" t="n">
-        <v>6779985</v>
+        <v>6780067</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5374,41 +5376,40 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131252336</v>
+        <v>131252313</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5418,10 +5419,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431610</v>
+        <v>431580</v>
       </c>
       <c r="R48" t="n">
-        <v>6780067</v>
+        <v>6779970</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5462,7 +5463,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131252295</v>
+        <v>131252322</v>
       </c>
       <c r="B49" t="n">
-        <v>79840</v>
+        <v>57885</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,26 +5492,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5519,10 +5524,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431735</v>
+        <v>431214</v>
       </c>
       <c r="R49" t="n">
-        <v>6780060</v>
+        <v>6779702</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5563,7 +5568,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5582,45 +5586,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252401</v>
+        <v>131252337</v>
       </c>
       <c r="B50" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431082</v>
+        <v>431622</v>
       </c>
       <c r="R50" t="n">
-        <v>6779651</v>
+        <v>6780061</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5655,17 +5668,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5684,45 +5693,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252395</v>
+        <v>131252352</v>
       </c>
       <c r="B51" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431310</v>
+        <v>431374</v>
       </c>
       <c r="R51" t="n">
-        <v>6779809</v>
+        <v>6779783</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5763,6 +5781,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5781,40 +5800,41 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252322</v>
+        <v>131252355</v>
       </c>
       <c r="B52" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5824,10 +5844,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431214</v>
+        <v>431356</v>
       </c>
       <c r="R52" t="n">
-        <v>6779702</v>
+        <v>6779743</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5868,6 +5888,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5886,43 +5907,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252337</v>
+        <v>131252295</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>79840</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5930,10 +5945,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431622</v>
+        <v>431735</v>
       </c>
       <c r="R53" t="n">
-        <v>6780061</v>
+        <v>6780060</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5993,51 +6008,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252352</v>
+        <v>131252324</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>79008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431374</v>
+        <v>431015</v>
       </c>
       <c r="R54" t="n">
         <v>6779783</v>
@@ -6081,7 +6087,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6100,54 +6105,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252355</v>
+        <v>131252401</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431356</v>
+        <v>431082</v>
       </c>
       <c r="R55" t="n">
-        <v>6779743</v>
+        <v>6779651</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6182,13 +6178,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252324</v>
+        <v>131252395</v>
       </c>
       <c r="B56" t="n">
-        <v>79008</v>
+        <v>79250</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6218,21 +6218,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431015</v>
+        <v>431310</v>
       </c>
       <c r="R56" t="n">
-        <v>6779783</v>
+        <v>6779809</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6304,7 +6304,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252376</v>
+        <v>131252397</v>
       </c>
       <c r="B57" t="n">
         <v>79250</v>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431316</v>
+        <v>431280</v>
       </c>
       <c r="R57" t="n">
-        <v>6779925</v>
+        <v>6779815</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,10 +6401,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131252397</v>
+        <v>131252312</v>
       </c>
       <c r="B58" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6412,34 +6412,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431280</v>
+        <v>431640</v>
       </c>
       <c r="R58" t="n">
-        <v>6779815</v>
+        <v>6780016</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,7 +6506,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131252312</v>
+        <v>131252320</v>
       </c>
       <c r="B59" t="n">
         <v>57885</v>
@@ -6541,10 +6549,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431640</v>
+        <v>431254</v>
       </c>
       <c r="R59" t="n">
-        <v>6780016</v>
+        <v>6779775</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6603,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131252320</v>
+        <v>131252376</v>
       </c>
       <c r="B60" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6614,42 +6622,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431254</v>
+        <v>431316</v>
       </c>
       <c r="R60" t="n">
-        <v>6779775</v>
+        <v>6779925</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131252301</v>
+        <v>131252385</v>
       </c>
       <c r="B62" t="n">
-        <v>58047</v>
+        <v>79250</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,42 +6820,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431747</v>
+        <v>431690</v>
       </c>
       <c r="R62" t="n">
-        <v>6780081</v>
+        <v>6780037</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6914,7 +6906,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131252385</v>
+        <v>131252398</v>
       </c>
       <c r="B63" t="n">
         <v>79250</v>
@@ -6949,10 +6941,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431690</v>
+        <v>431252</v>
       </c>
       <c r="R63" t="n">
-        <v>6780037</v>
+        <v>6779759</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7011,10 +7003,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131252398</v>
+        <v>131252301</v>
       </c>
       <c r="B64" t="n">
-        <v>79250</v>
+        <v>58047</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7022,34 +7014,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431252</v>
+        <v>431747</v>
       </c>
       <c r="R64" t="n">
-        <v>6779759</v>
+        <v>6780081</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7108,54 +7108,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131252328</v>
+        <v>131252360</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>79007</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431002</v>
+        <v>430970</v>
       </c>
       <c r="R65" t="n">
-        <v>6779756</v>
+        <v>6779700</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7196,7 +7187,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7215,43 +7205,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131252351</v>
+        <v>131252302</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>91839</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7259,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431370</v>
+        <v>431364</v>
       </c>
       <c r="R66" t="n">
-        <v>6779803</v>
+        <v>6779943</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7322,7 +7306,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131252354</v>
+        <v>131252328</v>
       </c>
       <c r="B67" t="n">
         <v>8451</v>
@@ -7356,7 +7340,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7366,10 +7350,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431358</v>
+        <v>431002</v>
       </c>
       <c r="R67" t="n">
-        <v>6779744</v>
+        <v>6779756</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7429,37 +7413,43 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131252302</v>
+        <v>131252351</v>
       </c>
       <c r="B68" t="n">
-        <v>91839</v>
+        <v>8451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7467,10 +7457,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431364</v>
+        <v>431370</v>
       </c>
       <c r="R68" t="n">
-        <v>6779943</v>
+        <v>6779803</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7530,45 +7520,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131252360</v>
+        <v>131252354</v>
       </c>
       <c r="B69" t="n">
-        <v>79007</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>430970</v>
+        <v>431358</v>
       </c>
       <c r="R69" t="n">
-        <v>6779700</v>
+        <v>6779744</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7609,6 +7608,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7627,54 +7627,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131252333</v>
+        <v>131252389</v>
       </c>
       <c r="B70" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431385</v>
+        <v>431389</v>
       </c>
       <c r="R70" t="n">
-        <v>6779961</v>
+        <v>6779928</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7715,7 +7706,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7734,7 +7724,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131252374</v>
+        <v>131252407</v>
       </c>
       <c r="B71" t="n">
         <v>79250</v>
@@ -7763,16 +7753,19 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431087</v>
+        <v>430942</v>
       </c>
       <c r="R71" t="n">
-        <v>6779811</v>
+        <v>6779693</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7813,6 +7806,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7831,7 +7825,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131252389</v>
+        <v>131252375</v>
       </c>
       <c r="B72" t="n">
         <v>79250</v>
@@ -7866,10 +7860,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431389</v>
+        <v>431294</v>
       </c>
       <c r="R72" t="n">
-        <v>6779928</v>
+        <v>6779898</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7928,7 +7922,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131252407</v>
+        <v>131252374</v>
       </c>
       <c r="B73" t="n">
         <v>79250</v>
@@ -7957,19 +7951,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>430942</v>
+        <v>431087</v>
       </c>
       <c r="R73" t="n">
-        <v>6779693</v>
+        <v>6779811</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8010,7 +8001,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8029,10 +8019,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131252375</v>
+        <v>131252314</v>
       </c>
       <c r="B74" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8040,34 +8030,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431294</v>
+        <v>431448</v>
       </c>
       <c r="R74" t="n">
-        <v>6779898</v>
+        <v>6779825</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8126,40 +8124,41 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252314</v>
+        <v>131252333</v>
       </c>
       <c r="B75" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8169,10 +8168,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431448</v>
+        <v>431385</v>
       </c>
       <c r="R75" t="n">
-        <v>6779825</v>
+        <v>6779961</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,6 +8212,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131252306</v>
+        <v>131252406</v>
       </c>
       <c r="B76" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8242,42 +8242,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430985</v>
+        <v>430975</v>
       </c>
       <c r="R76" t="n">
-        <v>6779728</v>
+        <v>6779698</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8336,40 +8328,41 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131252308</v>
+        <v>131252347</v>
       </c>
       <c r="B77" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8379,10 +8372,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431243</v>
+        <v>431446</v>
       </c>
       <c r="R77" t="n">
-        <v>6779888</v>
+        <v>6779877</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8423,6 +8416,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8441,45 +8435,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252406</v>
+        <v>131252349</v>
       </c>
       <c r="B78" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430975</v>
+        <v>431444</v>
       </c>
       <c r="R78" t="n">
-        <v>6779698</v>
+        <v>6779818</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8520,6 +8523,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8538,7 +8542,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131252347</v>
+        <v>131252345</v>
       </c>
       <c r="B79" t="n">
         <v>8451</v>
@@ -8572,7 +8576,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8582,10 +8586,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431446</v>
+        <v>431376</v>
       </c>
       <c r="R79" t="n">
-        <v>6779877</v>
+        <v>6779903</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,41 +8649,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131252349</v>
+        <v>131252306</v>
       </c>
       <c r="B80" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8689,10 +8692,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431444</v>
+        <v>430985</v>
       </c>
       <c r="R80" t="n">
-        <v>6779818</v>
+        <v>6779728</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8733,7 +8736,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8752,41 +8754,40 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131252345</v>
+        <v>131252308</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8796,10 +8797,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431376</v>
+        <v>431243</v>
       </c>
       <c r="R81" t="n">
-        <v>6779903</v>
+        <v>6779888</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,7 +8841,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9053,10 +9053,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131252404</v>
+        <v>131252315</v>
       </c>
       <c r="B84" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9064,34 +9064,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431024</v>
+        <v>431370</v>
       </c>
       <c r="R84" t="n">
-        <v>6779638</v>
+        <v>6779803</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9150,7 +9158,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131252380</v>
+        <v>131252404</v>
       </c>
       <c r="B85" t="n">
         <v>79250</v>
@@ -9185,10 +9193,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431673</v>
+        <v>431024</v>
       </c>
       <c r="R85" t="n">
-        <v>6780100</v>
+        <v>6779638</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9247,10 +9255,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131252315</v>
+        <v>131252380</v>
       </c>
       <c r="B86" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9258,42 +9266,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431370</v>
+        <v>431673</v>
       </c>
       <c r="R86" t="n">
-        <v>6779803</v>
+        <v>6780100</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9976,45 +9976,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131252293</v>
+        <v>131252327</v>
       </c>
       <c r="B93" t="n">
-        <v>79869</v>
+        <v>8451</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431669</v>
+        <v>431010</v>
       </c>
       <c r="R93" t="n">
-        <v>6780050</v>
+        <v>6779734</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10055,6 +10064,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10073,53 +10083,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131252300</v>
+        <v>131252293</v>
       </c>
       <c r="B94" t="n">
-        <v>57076</v>
+        <v>79869</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431560</v>
+        <v>431669</v>
       </c>
       <c r="R94" t="n">
-        <v>6779996</v>
+        <v>6780050</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10178,10 +10180,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131252327</v>
+        <v>131252300</v>
       </c>
       <c r="B95" t="n">
-        <v>8451</v>
+        <v>57076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10189,30 +10191,29 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10222,10 +10223,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431010</v>
+        <v>431560</v>
       </c>
       <c r="R95" t="n">
-        <v>6779734</v>
+        <v>6779996</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10266,7 +10267,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10285,54 +10285,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131252409</v>
+        <v>131252382</v>
       </c>
       <c r="B96" t="n">
-        <v>5177</v>
+        <v>79250</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431446</v>
+        <v>431806</v>
       </c>
       <c r="R96" t="n">
-        <v>6779877</v>
+        <v>6780050</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10373,7 +10364,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10392,54 +10382,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131252353</v>
+        <v>131252378</v>
       </c>
       <c r="B97" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431372</v>
+        <v>431561</v>
       </c>
       <c r="R97" t="n">
-        <v>6779775</v>
+        <v>6780045</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10480,7 +10461,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10499,7 +10479,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131252382</v>
+        <v>131252388</v>
       </c>
       <c r="B98" t="n">
         <v>79250</v>
@@ -10534,10 +10514,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431806</v>
+        <v>431442</v>
       </c>
       <c r="R98" t="n">
-        <v>6780050</v>
+        <v>6779937</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10596,45 +10576,54 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131252378</v>
+        <v>131252409</v>
       </c>
       <c r="B99" t="n">
-        <v>79250</v>
+        <v>5177</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431561</v>
+        <v>431446</v>
       </c>
       <c r="R99" t="n">
-        <v>6780045</v>
+        <v>6779877</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10675,6 +10664,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10794,45 +10784,54 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131252388</v>
+        <v>131252353</v>
       </c>
       <c r="B101" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431442</v>
+        <v>431372</v>
       </c>
       <c r="R101" t="n">
-        <v>6779937</v>
+        <v>6779775</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10873,6 +10872,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -1164,10 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131252303</v>
+        <v>131252319</v>
       </c>
       <c r="B7" t="n">
-        <v>91839</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,26 +1175,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1202,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431783</v>
+        <v>431343</v>
       </c>
       <c r="R7" t="n">
-        <v>6780157</v>
+        <v>6779764</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,7 +1251,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1265,40 +1269,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131252319</v>
+        <v>131252348</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1308,10 +1313,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431343</v>
+        <v>431502</v>
       </c>
       <c r="R8" t="n">
-        <v>6779764</v>
+        <v>6779842</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,6 +1357,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1370,43 +1376,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131252348</v>
+        <v>131252303</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>91839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431502</v>
+        <v>431783</v>
       </c>
       <c r="R9" t="n">
-        <v>6779842</v>
+        <v>6780157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131252393</v>
+        <v>131252317</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,34 +2003,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431431</v>
+        <v>431356</v>
       </c>
       <c r="R15" t="n">
-        <v>6779803</v>
+        <v>6779743</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,7 +2097,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131252390</v>
+        <v>131252393</v>
       </c>
       <c r="B16" t="n">
         <v>79250</v>
@@ -2124,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431416</v>
+        <v>431431</v>
       </c>
       <c r="R16" t="n">
-        <v>6779884</v>
+        <v>6779803</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2186,10 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131252317</v>
+        <v>131252390</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,42 +2205,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431356</v>
+        <v>431416</v>
       </c>
       <c r="R17" t="n">
-        <v>6779743</v>
+        <v>6779884</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131252396</v>
+        <v>131252386</v>
       </c>
       <c r="B22" t="n">
         <v>79250</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431284</v>
+        <v>431659</v>
       </c>
       <c r="R22" t="n">
-        <v>6779794</v>
+        <v>6780052</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131252392</v>
+        <v>131252321</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2827,34 +2827,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431477</v>
+        <v>431232</v>
       </c>
       <c r="R23" t="n">
-        <v>6779852</v>
+        <v>6779756</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2913,7 +2921,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131252371</v>
+        <v>131252396</v>
       </c>
       <c r="B24" t="n">
         <v>79250</v>
@@ -2948,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>430998</v>
+        <v>431284</v>
       </c>
       <c r="R24" t="n">
-        <v>6779729</v>
+        <v>6779794</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3010,7 +3018,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131252391</v>
+        <v>131252392</v>
       </c>
       <c r="B25" t="n">
         <v>79250</v>
@@ -3045,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431447</v>
+        <v>431477</v>
       </c>
       <c r="R25" t="n">
-        <v>6779876</v>
+        <v>6779852</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,7 +3115,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131252381</v>
+        <v>131252371</v>
       </c>
       <c r="B26" t="n">
         <v>79250</v>
@@ -3136,19 +3144,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431806</v>
+        <v>430998</v>
       </c>
       <c r="R26" t="n">
-        <v>6780109</v>
+        <v>6779729</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3189,7 +3194,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3208,7 +3212,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131252405</v>
+        <v>131252391</v>
       </c>
       <c r="B27" t="n">
         <v>79250</v>
@@ -3243,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430989</v>
+        <v>431447</v>
       </c>
       <c r="R27" t="n">
-        <v>6779656</v>
+        <v>6779876</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3279,11 +3283,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3310,7 +3309,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131252386</v>
+        <v>131252381</v>
       </c>
       <c r="B28" t="n">
         <v>79250</v>
@@ -3339,16 +3338,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431659</v>
+        <v>431806</v>
       </c>
       <c r="R28" t="n">
-        <v>6780052</v>
+        <v>6780109</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3389,6 +3391,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3407,10 +3410,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131252321</v>
+        <v>131252405</v>
       </c>
       <c r="B29" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3418,42 +3421,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431232</v>
+        <v>430989</v>
       </c>
       <c r="R29" t="n">
-        <v>6779756</v>
+        <v>6779656</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3486,6 +3481,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3724,54 +3724,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131252346</v>
+        <v>131252403</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431434</v>
+        <v>431055</v>
       </c>
       <c r="R32" t="n">
-        <v>6779875</v>
+        <v>6779612</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,13 +3797,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3831,54 +3826,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131252414</v>
+        <v>131252384</v>
       </c>
       <c r="B33" t="n">
-        <v>8440</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431245</v>
+        <v>431710</v>
       </c>
       <c r="R33" t="n">
-        <v>6779803</v>
+        <v>6780009</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3913,13 +3899,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3938,41 +3928,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131252357</v>
+        <v>131252316</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3982,10 +3971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431074</v>
+        <v>431357</v>
       </c>
       <c r="R34" t="n">
-        <v>6779685</v>
+        <v>6779763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4026,7 +4015,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4045,45 +4033,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131252403</v>
+        <v>131252346</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431055</v>
+        <v>431434</v>
       </c>
       <c r="R35" t="n">
-        <v>6779612</v>
+        <v>6779875</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4118,17 +4115,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4147,45 +4140,54 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131252384</v>
+        <v>131252414</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>8440</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431710</v>
+        <v>431245</v>
       </c>
       <c r="R36" t="n">
-        <v>6780009</v>
+        <v>6779803</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4220,17 +4222,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4249,40 +4247,41 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131252316</v>
+        <v>131252357</v>
       </c>
       <c r="B37" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4292,10 +4291,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431357</v>
+        <v>431074</v>
       </c>
       <c r="R37" t="n">
-        <v>6779763</v>
+        <v>6779685</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4336,6 +4335,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4560,54 +4560,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131252339</v>
+        <v>131252373</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431754</v>
+        <v>431077</v>
       </c>
       <c r="R40" t="n">
-        <v>6780143</v>
+        <v>6779777</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4648,7 +4639,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4667,54 +4657,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131252341</v>
+        <v>131252372</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431684</v>
+        <v>431053</v>
       </c>
       <c r="R41" t="n">
-        <v>6780041</v>
+        <v>6779790</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,7 +4736,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4774,7 +4754,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131252373</v>
+        <v>131252387</v>
       </c>
       <c r="B42" t="n">
         <v>79250</v>
@@ -4809,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431077</v>
+        <v>431622</v>
       </c>
       <c r="R42" t="n">
-        <v>6779777</v>
+        <v>6780004</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4871,45 +4851,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131252372</v>
+        <v>131252339</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431053</v>
+        <v>431754</v>
       </c>
       <c r="R43" t="n">
-        <v>6779790</v>
+        <v>6780143</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4950,6 +4939,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4968,45 +4958,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131252387</v>
+        <v>131252341</v>
       </c>
       <c r="B44" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431622</v>
+        <v>431684</v>
       </c>
       <c r="R44" t="n">
-        <v>6780004</v>
+        <v>6780041</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5047,6 +5046,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5586,54 +5586,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252337</v>
+        <v>131252401</v>
       </c>
       <c r="B50" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431622</v>
+        <v>431082</v>
       </c>
       <c r="R50" t="n">
-        <v>6780061</v>
+        <v>6779651</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5668,13 +5659,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5693,54 +5688,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252352</v>
+        <v>131252395</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431374</v>
+        <v>431310</v>
       </c>
       <c r="R51" t="n">
-        <v>6779783</v>
+        <v>6779809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5781,7 +5767,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5800,43 +5785,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252355</v>
+        <v>131252295</v>
       </c>
       <c r="B52" t="n">
-        <v>8451</v>
+        <v>79840</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5844,10 +5823,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431356</v>
+        <v>431735</v>
       </c>
       <c r="R52" t="n">
-        <v>6779743</v>
+        <v>6780060</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5907,10 +5886,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252295</v>
+        <v>131252324</v>
       </c>
       <c r="B53" t="n">
-        <v>79840</v>
+        <v>79008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5918,37 +5897,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431735</v>
+        <v>431015</v>
       </c>
       <c r="R53" t="n">
-        <v>6780060</v>
+        <v>6779783</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5989,7 +5965,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6008,45 +5983,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252324</v>
+        <v>131252337</v>
       </c>
       <c r="B54" t="n">
-        <v>79008</v>
+        <v>8451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431015</v>
+        <v>431622</v>
       </c>
       <c r="R54" t="n">
-        <v>6779783</v>
+        <v>6780061</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6087,6 +6071,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6105,45 +6090,54 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252401</v>
+        <v>131252352</v>
       </c>
       <c r="B55" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431082</v>
+        <v>431374</v>
       </c>
       <c r="R55" t="n">
-        <v>6779651</v>
+        <v>6779783</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6178,17 +6172,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6207,45 +6197,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252395</v>
+        <v>131252355</v>
       </c>
       <c r="B56" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431310</v>
+        <v>431356</v>
       </c>
       <c r="R56" t="n">
-        <v>6779809</v>
+        <v>6779743</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6286,6 +6285,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252397</v>
+        <v>131252326</v>
       </c>
       <c r="B57" t="n">
-        <v>79250</v>
+        <v>79008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,34 +6315,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431280</v>
+        <v>431339</v>
       </c>
       <c r="R57" t="n">
-        <v>6779815</v>
+        <v>6779765</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6383,6 +6386,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6401,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131252312</v>
+        <v>131252397</v>
       </c>
       <c r="B58" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6412,42 +6416,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431640</v>
+        <v>431280</v>
       </c>
       <c r="R58" t="n">
-        <v>6780016</v>
+        <v>6779815</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6506,7 +6502,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131252320</v>
+        <v>131252312</v>
       </c>
       <c r="B59" t="n">
         <v>57885</v>
@@ -6549,10 +6545,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>431254</v>
+        <v>431640</v>
       </c>
       <c r="R59" t="n">
-        <v>6779775</v>
+        <v>6780016</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6611,10 +6607,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131252376</v>
+        <v>131252320</v>
       </c>
       <c r="B60" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6622,34 +6618,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431316</v>
+        <v>431254</v>
       </c>
       <c r="R60" t="n">
-        <v>6779925</v>
+        <v>6779775</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6708,10 +6712,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131252326</v>
+        <v>131252376</v>
       </c>
       <c r="B61" t="n">
-        <v>79008</v>
+        <v>79250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6719,37 +6723,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431339</v>
+        <v>431316</v>
       </c>
       <c r="R61" t="n">
-        <v>6779765</v>
+        <v>6779925</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6790,7 +6791,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7627,45 +7627,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131252389</v>
+        <v>131252333</v>
       </c>
       <c r="B70" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431389</v>
+        <v>431385</v>
       </c>
       <c r="R70" t="n">
-        <v>6779928</v>
+        <v>6779961</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7706,6 +7715,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7724,7 +7734,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131252407</v>
+        <v>131252389</v>
       </c>
       <c r="B71" t="n">
         <v>79250</v>
@@ -7753,19 +7763,16 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430942</v>
+        <v>431389</v>
       </c>
       <c r="R71" t="n">
-        <v>6779693</v>
+        <v>6779928</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7806,7 +7813,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7825,7 +7831,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131252375</v>
+        <v>131252407</v>
       </c>
       <c r="B72" t="n">
         <v>79250</v>
@@ -7854,16 +7860,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431294</v>
+        <v>430942</v>
       </c>
       <c r="R72" t="n">
-        <v>6779898</v>
+        <v>6779693</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7904,6 +7913,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7922,7 +7932,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131252374</v>
+        <v>131252375</v>
       </c>
       <c r="B73" t="n">
         <v>79250</v>
@@ -7957,10 +7967,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431087</v>
+        <v>431294</v>
       </c>
       <c r="R73" t="n">
-        <v>6779811</v>
+        <v>6779898</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8124,54 +8134,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252333</v>
+        <v>131252374</v>
       </c>
       <c r="B75" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431385</v>
+        <v>431087</v>
       </c>
       <c r="R75" t="n">
-        <v>6779961</v>
+        <v>6779811</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8212,7 +8213,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8231,45 +8231,54 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131252406</v>
+        <v>131252347</v>
       </c>
       <c r="B76" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430975</v>
+        <v>431446</v>
       </c>
       <c r="R76" t="n">
-        <v>6779698</v>
+        <v>6779877</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8310,6 +8319,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8328,7 +8338,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131252347</v>
+        <v>131252349</v>
       </c>
       <c r="B77" t="n">
         <v>8451</v>
@@ -8362,7 +8372,7 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8372,10 +8382,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431446</v>
+        <v>431444</v>
       </c>
       <c r="R77" t="n">
-        <v>6779877</v>
+        <v>6779818</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8435,7 +8445,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252349</v>
+        <v>131252345</v>
       </c>
       <c r="B78" t="n">
         <v>8451</v>
@@ -8469,7 +8479,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8479,10 +8489,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431444</v>
+        <v>431376</v>
       </c>
       <c r="R78" t="n">
-        <v>6779818</v>
+        <v>6779903</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8542,41 +8552,40 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131252345</v>
+        <v>131252306</v>
       </c>
       <c r="B79" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8586,10 +8595,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431376</v>
+        <v>430985</v>
       </c>
       <c r="R79" t="n">
-        <v>6779903</v>
+        <v>6779728</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8630,7 +8639,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8649,7 +8657,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131252306</v>
+        <v>131252308</v>
       </c>
       <c r="B80" t="n">
         <v>57885</v>
@@ -8692,10 +8700,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>430985</v>
+        <v>431243</v>
       </c>
       <c r="R80" t="n">
-        <v>6779728</v>
+        <v>6779888</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8754,10 +8762,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131252308</v>
+        <v>131252406</v>
       </c>
       <c r="B81" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8765,42 +8773,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431243</v>
+        <v>430975</v>
       </c>
       <c r="R81" t="n">
-        <v>6779888</v>
+        <v>6779698</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10683,37 +10683,43 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131252305</v>
+        <v>131252353</v>
       </c>
       <c r="B100" t="n">
-        <v>91839</v>
+        <v>8451</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -10721,10 +10727,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431438</v>
+        <v>431372</v>
       </c>
       <c r="R100" t="n">
-        <v>6779872</v>
+        <v>6779775</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10784,43 +10790,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131252353</v>
+        <v>131252305</v>
       </c>
       <c r="B101" t="n">
-        <v>8451</v>
+        <v>91839</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431372</v>
+        <v>431438</v>
       </c>
       <c r="R101" t="n">
-        <v>6779775</v>
+        <v>6779872</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131252377</v>
       </c>
       <c r="B2" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131252402</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>131252370</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>131252359</v>
       </c>
       <c r="B5" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>131252408</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>131252319</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>131252348</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>131252303</v>
       </c>
       <c r="B9" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131252400</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>131252294</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>79872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>131252343</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>131252344</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>131252358</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131252317</v>
+        <v>131252393</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,42 +2003,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431356</v>
+        <v>431431</v>
       </c>
       <c r="R15" t="n">
-        <v>6779743</v>
+        <v>6779803</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131252393</v>
+        <v>131252390</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431431</v>
+        <v>431416</v>
       </c>
       <c r="R16" t="n">
-        <v>6779803</v>
+        <v>6779884</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,10 +2186,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131252390</v>
+        <v>131252317</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2205,34 +2197,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431416</v>
+        <v>431356</v>
       </c>
       <c r="R17" t="n">
-        <v>6779884</v>
+        <v>6779743</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,7 +2294,7 @@
         <v>131252413</v>
       </c>
       <c r="B18" t="n">
-        <v>8440</v>
+        <v>8442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>131252342</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>131252334</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>131252350</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131252386</v>
+        <v>131252396</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431659</v>
+        <v>431284</v>
       </c>
       <c r="R22" t="n">
-        <v>6780052</v>
+        <v>6779794</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131252321</v>
+        <v>131252392</v>
       </c>
       <c r="B23" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2827,42 +2827,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431232</v>
+        <v>431477</v>
       </c>
       <c r="R23" t="n">
-        <v>6779756</v>
+        <v>6779852</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,10 +2913,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131252396</v>
+        <v>131252386</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2956,10 +2948,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431284</v>
+        <v>431659</v>
       </c>
       <c r="R24" t="n">
-        <v>6779794</v>
+        <v>6780052</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,10 +3010,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131252392</v>
+        <v>131252371</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,10 +3045,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>431477</v>
+        <v>430998</v>
       </c>
       <c r="R25" t="n">
-        <v>6779852</v>
+        <v>6779729</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,10 +3107,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131252371</v>
+        <v>131252391</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,10 +3142,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>430998</v>
+        <v>431447</v>
       </c>
       <c r="R26" t="n">
-        <v>6779729</v>
+        <v>6779876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,10 +3204,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131252391</v>
+        <v>131252405</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3247,10 +3239,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>431447</v>
+        <v>430989</v>
       </c>
       <c r="R27" t="n">
-        <v>6779876</v>
+        <v>6779656</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,6 +3275,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3309,10 +3306,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131252381</v>
+        <v>131252321</v>
       </c>
       <c r="B28" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,26 +3317,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3347,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431806</v>
+        <v>431232</v>
       </c>
       <c r="R28" t="n">
-        <v>6780109</v>
+        <v>6779756</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3391,7 +3393,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3410,10 +3411,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131252405</v>
+        <v>131252381</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,16 +3440,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>430989</v>
+        <v>431806</v>
       </c>
       <c r="R29" t="n">
-        <v>6779656</v>
+        <v>6780109</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,17 +3487,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>131252309</v>
       </c>
       <c r="B30" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>131252332</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>131252403</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>131252384</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>131252316</v>
       </c>
       <c r="B34" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>131252346</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>131252414</v>
       </c>
       <c r="B36" t="n">
-        <v>8440</v>
+        <v>8442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>131252357</v>
       </c>
       <c r="B37" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>131252325</v>
       </c>
       <c r="B38" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131252311</v>
+        <v>131252372</v>
       </c>
       <c r="B39" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,42 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431487</v>
+        <v>431053</v>
       </c>
       <c r="R39" t="n">
-        <v>6779989</v>
+        <v>6779790</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4560,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131252373</v>
+        <v>131252387</v>
       </c>
       <c r="B40" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4595,10 +4587,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431077</v>
+        <v>431622</v>
       </c>
       <c r="R40" t="n">
-        <v>6779777</v>
+        <v>6780004</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131252372</v>
+        <v>131252373</v>
       </c>
       <c r="B41" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4692,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431053</v>
+        <v>431077</v>
       </c>
       <c r="R41" t="n">
-        <v>6779790</v>
+        <v>6779777</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4754,10 +4746,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131252387</v>
+        <v>131252311</v>
       </c>
       <c r="B42" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4765,34 +4757,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>431622</v>
+        <v>431487</v>
       </c>
       <c r="R42" t="n">
-        <v>6780004</v>
+        <v>6779989</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4854,7 +4854,7 @@
         <v>131252339</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>131252341</v>
       </c>
       <c r="B44" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>131252399</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>131252340</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>131252336</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>131252313</v>
       </c>
       <c r="B48" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131252322</v>
+        <v>131252395</v>
       </c>
       <c r="B49" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,42 +5492,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431214</v>
+        <v>431310</v>
       </c>
       <c r="R49" t="n">
-        <v>6779702</v>
+        <v>6779809</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5589,7 +5581,7 @@
         <v>131252401</v>
       </c>
       <c r="B50" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5688,10 +5680,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252395</v>
+        <v>131252322</v>
       </c>
       <c r="B51" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5699,34 +5691,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431310</v>
+        <v>431214</v>
       </c>
       <c r="R51" t="n">
-        <v>6779809</v>
+        <v>6779702</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5785,37 +5785,43 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252295</v>
+        <v>131252337</v>
       </c>
       <c r="B52" t="n">
-        <v>79840</v>
+        <v>8453</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5823,10 +5829,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431735</v>
+        <v>431622</v>
       </c>
       <c r="R52" t="n">
-        <v>6780060</v>
+        <v>6780061</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5886,42 +5892,51 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252324</v>
+        <v>131252352</v>
       </c>
       <c r="B53" t="n">
-        <v>79008</v>
+        <v>8453</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431015</v>
+        <v>431374</v>
       </c>
       <c r="R53" t="n">
         <v>6779783</v>
@@ -5965,6 +5980,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5983,10 +5999,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252337</v>
+        <v>131252355</v>
       </c>
       <c r="B54" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6027,10 +6043,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431622</v>
+        <v>431356</v>
       </c>
       <c r="R54" t="n">
-        <v>6780061</v>
+        <v>6779743</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6090,43 +6106,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252352</v>
+        <v>131252295</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>79843</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6134,10 +6144,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431374</v>
+        <v>431735</v>
       </c>
       <c r="R55" t="n">
-        <v>6779783</v>
+        <v>6780060</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6197,54 +6207,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252355</v>
+        <v>131252324</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431356</v>
+        <v>431015</v>
       </c>
       <c r="R56" t="n">
-        <v>6779743</v>
+        <v>6779783</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,7 +6286,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252326</v>
+        <v>131252376</v>
       </c>
       <c r="B57" t="n">
-        <v>79008</v>
+        <v>79253</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6315,37 +6315,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431339</v>
+        <v>431316</v>
       </c>
       <c r="R57" t="n">
-        <v>6779765</v>
+        <v>6779925</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6386,7 +6383,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6408,7 +6404,7 @@
         <v>131252397</v>
       </c>
       <c r="B58" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6505,7 +6501,7 @@
         <v>131252312</v>
       </c>
       <c r="B59" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6610,7 +6606,7 @@
         <v>131252320</v>
       </c>
       <c r="B60" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6712,10 +6708,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131252376</v>
+        <v>131252326</v>
       </c>
       <c r="B61" t="n">
-        <v>79250</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6723,34 +6719,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431316</v>
+        <v>431339</v>
       </c>
       <c r="R61" t="n">
-        <v>6779925</v>
+        <v>6779765</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6791,6 +6790,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>131252385</v>
       </c>
       <c r="B62" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>131252398</v>
       </c>
       <c r="B63" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>131252301</v>
       </c>
       <c r="B64" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7108,10 +7108,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131252360</v>
+        <v>131252302</v>
       </c>
       <c r="B65" t="n">
-        <v>79007</v>
+        <v>91842</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7119,34 +7119,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>430970</v>
+        <v>431364</v>
       </c>
       <c r="R65" t="n">
-        <v>6779700</v>
+        <v>6779943</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7187,6 +7190,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7205,10 +7209,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131252302</v>
+        <v>131252360</v>
       </c>
       <c r="B66" t="n">
-        <v>91839</v>
+        <v>79010</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7216,37 +7220,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>431364</v>
+        <v>430970</v>
       </c>
       <c r="R66" t="n">
-        <v>6779943</v>
+        <v>6779700</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7287,7 +7288,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7309,7 +7309,7 @@
         <v>131252328</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>131252351</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>131252354</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7627,41 +7627,40 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131252333</v>
+        <v>131252314</v>
       </c>
       <c r="B70" t="n">
-        <v>8451</v>
+        <v>57888</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7671,10 +7670,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431385</v>
+        <v>431448</v>
       </c>
       <c r="R70" t="n">
-        <v>6779961</v>
+        <v>6779825</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7715,7 +7714,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7734,45 +7732,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131252389</v>
+        <v>131252333</v>
       </c>
       <c r="B71" t="n">
-        <v>79250</v>
+        <v>8453</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431389</v>
+        <v>431385</v>
       </c>
       <c r="R71" t="n">
-        <v>6779928</v>
+        <v>6779961</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7813,6 +7820,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7831,10 +7839,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131252407</v>
+        <v>131252374</v>
       </c>
       <c r="B72" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7860,19 +7868,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>430942</v>
+        <v>431087</v>
       </c>
       <c r="R72" t="n">
-        <v>6779693</v>
+        <v>6779811</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7913,7 +7918,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7932,10 +7936,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131252375</v>
+        <v>131252389</v>
       </c>
       <c r="B73" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7967,10 +7971,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431294</v>
+        <v>431389</v>
       </c>
       <c r="R73" t="n">
-        <v>6779898</v>
+        <v>6779928</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8029,10 +8033,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131252314</v>
+        <v>131252407</v>
       </c>
       <c r="B74" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8040,31 +8044,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8072,10 +8071,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431448</v>
+        <v>430942</v>
       </c>
       <c r="R74" t="n">
-        <v>6779825</v>
+        <v>6779693</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8116,6 +8115,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8134,10 +8134,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252374</v>
+        <v>131252375</v>
       </c>
       <c r="B75" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8169,10 +8169,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431087</v>
+        <v>431294</v>
       </c>
       <c r="R75" t="n">
-        <v>6779811</v>
+        <v>6779898</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8231,41 +8231,40 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131252347</v>
+        <v>131252306</v>
       </c>
       <c r="B76" t="n">
-        <v>8451</v>
+        <v>57888</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
@@ -8275,10 +8274,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>431446</v>
+        <v>430985</v>
       </c>
       <c r="R76" t="n">
-        <v>6779877</v>
+        <v>6779728</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8319,7 +8318,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8338,41 +8336,40 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131252349</v>
+        <v>131252308</v>
       </c>
       <c r="B77" t="n">
-        <v>8451</v>
+        <v>57888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8382,10 +8379,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431444</v>
+        <v>431243</v>
       </c>
       <c r="R77" t="n">
-        <v>6779818</v>
+        <v>6779888</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8426,7 +8423,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8445,54 +8441,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252345</v>
+        <v>131252406</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>79253</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>431376</v>
+        <v>430975</v>
       </c>
       <c r="R78" t="n">
-        <v>6779903</v>
+        <v>6779698</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8533,7 +8520,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8552,40 +8538,41 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131252306</v>
+        <v>131252347</v>
       </c>
       <c r="B79" t="n">
-        <v>57885</v>
+        <v>8453</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8595,10 +8582,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>430985</v>
+        <v>431446</v>
       </c>
       <c r="R79" t="n">
-        <v>6779728</v>
+        <v>6779877</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8639,6 +8626,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8657,40 +8645,41 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131252308</v>
+        <v>131252349</v>
       </c>
       <c r="B80" t="n">
-        <v>57885</v>
+        <v>8453</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8700,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431243</v>
+        <v>431444</v>
       </c>
       <c r="R80" t="n">
-        <v>6779888</v>
+        <v>6779818</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8744,6 +8733,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8762,45 +8752,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131252406</v>
+        <v>131252345</v>
       </c>
       <c r="B81" t="n">
-        <v>79250</v>
+        <v>8453</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>430975</v>
+        <v>431376</v>
       </c>
       <c r="R81" t="n">
-        <v>6779698</v>
+        <v>6779903</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8841,6 +8840,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>131252383</v>
       </c>
       <c r="B82" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>131252379</v>
       </c>
       <c r="B83" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9053,10 +9053,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131252315</v>
+        <v>131252404</v>
       </c>
       <c r="B84" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9064,42 +9064,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>431370</v>
+        <v>431024</v>
       </c>
       <c r="R84" t="n">
-        <v>6779803</v>
+        <v>6779638</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9158,10 +9150,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131252404</v>
+        <v>131252380</v>
       </c>
       <c r="B85" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9193,10 +9185,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>431024</v>
+        <v>431673</v>
       </c>
       <c r="R85" t="n">
-        <v>6779638</v>
+        <v>6780100</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9255,10 +9247,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131252380</v>
+        <v>131252315</v>
       </c>
       <c r="B86" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9266,34 +9258,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431673</v>
+        <v>431370</v>
       </c>
       <c r="R86" t="n">
-        <v>6780100</v>
+        <v>6779803</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9355,7 +9355,7 @@
         <v>131252335</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>131252304</v>
       </c>
       <c r="B88" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>131252323</v>
       </c>
       <c r="B89" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9665,45 +9665,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131252394</v>
+        <v>131252331</v>
       </c>
       <c r="B90" t="n">
-        <v>79250</v>
+        <v>8453</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431327</v>
+        <v>431291</v>
       </c>
       <c r="R90" t="n">
-        <v>6779796</v>
+        <v>6779892</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9744,6 +9753,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9762,10 +9772,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131252331</v>
+        <v>131252330</v>
       </c>
       <c r="B91" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9806,10 +9816,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431291</v>
+        <v>431075</v>
       </c>
       <c r="R91" t="n">
-        <v>6779892</v>
+        <v>6779775</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9869,54 +9879,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131252330</v>
+        <v>131252394</v>
       </c>
       <c r="B92" t="n">
-        <v>8451</v>
+        <v>79253</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431075</v>
+        <v>431327</v>
       </c>
       <c r="R92" t="n">
-        <v>6779775</v>
+        <v>6779796</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9957,7 +9958,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9976,54 +9976,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131252327</v>
+        <v>131252293</v>
       </c>
       <c r="B93" t="n">
-        <v>8451</v>
+        <v>79872</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431010</v>
+        <v>431669</v>
       </c>
       <c r="R93" t="n">
-        <v>6779734</v>
+        <v>6780050</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10064,7 +10055,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10083,45 +10073,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131252293</v>
+        <v>131252300</v>
       </c>
       <c r="B94" t="n">
-        <v>79869</v>
+        <v>57079</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431669</v>
+        <v>431560</v>
       </c>
       <c r="R94" t="n">
-        <v>6780050</v>
+        <v>6779996</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10180,10 +10178,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131252300</v>
+        <v>131252327</v>
       </c>
       <c r="B95" t="n">
-        <v>57076</v>
+        <v>8453</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10191,29 +10189,30 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10223,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431560</v>
+        <v>431010</v>
       </c>
       <c r="R95" t="n">
-        <v>6779996</v>
+        <v>6779734</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10267,6 +10266,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131252382</v>
+        <v>131252378</v>
       </c>
       <c r="B96" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431806</v>
+        <v>431561</v>
       </c>
       <c r="R96" t="n">
-        <v>6780050</v>
+        <v>6780045</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10382,10 +10382,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131252378</v>
+        <v>131252305</v>
       </c>
       <c r="B97" t="n">
-        <v>79250</v>
+        <v>91842</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10393,34 +10393,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431561</v>
+        <v>431438</v>
       </c>
       <c r="R97" t="n">
-        <v>6780045</v>
+        <v>6779872</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10461,6 +10464,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10482,7 +10486,7 @@
         <v>131252388</v>
       </c>
       <c r="B98" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10576,54 +10580,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131252409</v>
+        <v>131252382</v>
       </c>
       <c r="B99" t="n">
-        <v>5177</v>
+        <v>79253</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431446</v>
+        <v>431806</v>
       </c>
       <c r="R99" t="n">
-        <v>6779877</v>
+        <v>6780050</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10664,7 +10659,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10683,10 +10677,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131252353</v>
+        <v>131252409</v>
       </c>
       <c r="B100" t="n">
-        <v>8451</v>
+        <v>5177</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10694,21 +10688,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10717,7 +10711,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -10727,10 +10721,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>431372</v>
+        <v>431446</v>
       </c>
       <c r="R100" t="n">
-        <v>6779775</v>
+        <v>6779877</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10790,37 +10784,43 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131252305</v>
+        <v>131252353</v>
       </c>
       <c r="B101" t="n">
-        <v>91839</v>
+        <v>8453</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -10828,10 +10828,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>431438</v>
+        <v>431372</v>
       </c>
       <c r="R101" t="n">
-        <v>6779872</v>
+        <v>6779775</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131252377</v>
       </c>
       <c r="B2" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131252402</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>131252370</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>131252359</v>
       </c>
       <c r="B5" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>131252408</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>131252319</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>131252303</v>
       </c>
       <c r="B9" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131252400</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>131252294</v>
       </c>
       <c r="B11" t="n">
-        <v>79872</v>
+        <v>79873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1992,45 +1992,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131252393</v>
+        <v>131252413</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>8442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>431431</v>
+        <v>431288</v>
       </c>
       <c r="R15" t="n">
-        <v>6779803</v>
+        <v>6779800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,6 +2080,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2089,45 +2099,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131252390</v>
+        <v>131252342</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>8453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>431416</v>
+        <v>431644</v>
       </c>
       <c r="R16" t="n">
-        <v>6779884</v>
+        <v>6780041</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,6 +2187,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2186,40 +2206,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131252317</v>
+        <v>131252334</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2229,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>431356</v>
+        <v>431411</v>
       </c>
       <c r="R17" t="n">
-        <v>6779743</v>
+        <v>6779968</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,6 +2294,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2291,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131252413</v>
+        <v>131252350</v>
       </c>
       <c r="B18" t="n">
-        <v>8442</v>
+        <v>8453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2302,21 +2324,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2335,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>431288</v>
+        <v>431430</v>
       </c>
       <c r="R18" t="n">
-        <v>6779800</v>
+        <v>6779818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,54 +2420,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131252342</v>
+        <v>131252393</v>
       </c>
       <c r="B19" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>431644</v>
+        <v>431431</v>
       </c>
       <c r="R19" t="n">
-        <v>6780041</v>
+        <v>6779803</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,7 +2499,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2505,54 +2517,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131252334</v>
+        <v>131252390</v>
       </c>
       <c r="B20" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>431411</v>
+        <v>431416</v>
       </c>
       <c r="R20" t="n">
-        <v>6779968</v>
+        <v>6779884</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,7 +2596,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2612,41 +2614,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131252350</v>
+        <v>131252317</v>
       </c>
       <c r="B21" t="n">
-        <v>8453</v>
+        <v>57889</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2656,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>431430</v>
+        <v>431356</v>
       </c>
       <c r="R21" t="n">
-        <v>6779818</v>
+        <v>6779743</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2700,7 +2701,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131252396</v>
+        <v>131252386</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>431284</v>
+        <v>431659</v>
       </c>
       <c r="R22" t="n">
-        <v>6779794</v>
+        <v>6780052</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131252392</v>
+        <v>131252371</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>431477</v>
+        <v>430998</v>
       </c>
       <c r="R23" t="n">
-        <v>6779852</v>
+        <v>6779729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131252386</v>
+        <v>131252391</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>431659</v>
+        <v>431447</v>
       </c>
       <c r="R24" t="n">
-        <v>6780052</v>
+        <v>6779876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3010,10 +3010,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131252371</v>
+        <v>131252396</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>430998</v>
+        <v>431284</v>
       </c>
       <c r="R25" t="n">
-        <v>6779729</v>
+        <v>6779794</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131252391</v>
+        <v>131252392</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>431447</v>
+        <v>431477</v>
       </c>
       <c r="R26" t="n">
-        <v>6779876</v>
+        <v>6779852</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,10 +3204,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131252405</v>
+        <v>131252381</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,16 +3233,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>430989</v>
+        <v>431806</v>
       </c>
       <c r="R27" t="n">
-        <v>6779656</v>
+        <v>6780109</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3277,17 +3280,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50m.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3306,10 +3305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131252321</v>
+        <v>131252405</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3317,42 +3316,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>431232</v>
+        <v>430989</v>
       </c>
       <c r="R28" t="n">
-        <v>6779756</v>
+        <v>6779656</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3385,6 +3376,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,10 +3407,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131252381</v>
+        <v>131252321</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3422,26 +3418,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3449,10 +3450,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>431806</v>
+        <v>431232</v>
       </c>
       <c r="R29" t="n">
-        <v>6780109</v>
+        <v>6779756</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3493,7 +3494,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>131252309</v>
       </c>
       <c r="B30" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>131252403</v>
       </c>
       <c r="B32" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>131252384</v>
       </c>
       <c r="B33" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,40 +3928,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131252316</v>
+        <v>131252346</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3971,10 +3972,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431357</v>
+        <v>431434</v>
       </c>
       <c r="R34" t="n">
-        <v>6779763</v>
+        <v>6779875</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4015,6 +4016,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4033,10 +4035,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131252346</v>
+        <v>131252414</v>
       </c>
       <c r="B35" t="n">
-        <v>8453</v>
+        <v>8442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,21 +4046,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4077,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431434</v>
+        <v>431245</v>
       </c>
       <c r="R35" t="n">
-        <v>6779875</v>
+        <v>6779803</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4140,10 +4142,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131252414</v>
+        <v>131252357</v>
       </c>
       <c r="B36" t="n">
-        <v>8442</v>
+        <v>8453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4151,21 +4153,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4184,10 +4186,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431245</v>
+        <v>431074</v>
       </c>
       <c r="R36" t="n">
-        <v>6779803</v>
+        <v>6779685</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,43 +4249,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131252357</v>
+        <v>131252325</v>
       </c>
       <c r="B37" t="n">
-        <v>8453</v>
+        <v>79012</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4291,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431074</v>
+        <v>431743</v>
       </c>
       <c r="R37" t="n">
-        <v>6779685</v>
+        <v>6780091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4354,10 +4350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131252325</v>
+        <v>131252316</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>57889</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4365,26 +4361,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4392,10 +4393,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431743</v>
+        <v>431357</v>
       </c>
       <c r="R38" t="n">
-        <v>6780091</v>
+        <v>6779763</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4436,7 +4437,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131252372</v>
+        <v>131252373</v>
       </c>
       <c r="B39" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>431053</v>
+        <v>431077</v>
       </c>
       <c r="R39" t="n">
-        <v>6779790</v>
+        <v>6779777</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131252387</v>
+        <v>131252372</v>
       </c>
       <c r="B40" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>431622</v>
+        <v>431053</v>
       </c>
       <c r="R40" t="n">
-        <v>6780004</v>
+        <v>6779790</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4649,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131252373</v>
+        <v>131252387</v>
       </c>
       <c r="B41" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>431077</v>
+        <v>431622</v>
       </c>
       <c r="R41" t="n">
-        <v>6779777</v>
+        <v>6780004</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4749,7 +4749,7 @@
         <v>131252311</v>
       </c>
       <c r="B42" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131252339</v>
+        <v>131252341</v>
       </c>
       <c r="B43" t="n">
         <v>8453</v>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431754</v>
+        <v>431684</v>
       </c>
       <c r="R43" t="n">
-        <v>6780143</v>
+        <v>6780041</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4958,7 +4958,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131252341</v>
+        <v>131252339</v>
       </c>
       <c r="B44" t="n">
         <v>8453</v>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431684</v>
+        <v>431754</v>
       </c>
       <c r="R44" t="n">
-        <v>6780041</v>
+        <v>6780143</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131252399</v>
+        <v>131252313</v>
       </c>
       <c r="B45" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,34 +5076,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>431257</v>
+        <v>431580</v>
       </c>
       <c r="R45" t="n">
-        <v>6779698</v>
+        <v>6779970</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5162,54 +5170,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131252340</v>
+        <v>131252399</v>
       </c>
       <c r="B46" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>431705</v>
+        <v>431257</v>
       </c>
       <c r="R46" t="n">
-        <v>6779985</v>
+        <v>6779698</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5250,7 +5249,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5269,7 +5267,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131252336</v>
+        <v>131252340</v>
       </c>
       <c r="B47" t="n">
         <v>8453</v>
@@ -5303,7 +5301,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5313,10 +5311,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>431610</v>
+        <v>431705</v>
       </c>
       <c r="R47" t="n">
-        <v>6780067</v>
+        <v>6779985</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5376,40 +5374,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131252313</v>
+        <v>131252336</v>
       </c>
       <c r="B48" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5419,10 +5418,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>431580</v>
+        <v>431610</v>
       </c>
       <c r="R48" t="n">
-        <v>6779970</v>
+        <v>6780067</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5463,6 +5462,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131252395</v>
+        <v>131252401</v>
       </c>
       <c r="B49" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431310</v>
+        <v>431082</v>
       </c>
       <c r="R49" t="n">
-        <v>6779809</v>
+        <v>6779651</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5552,6 +5552,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5578,10 +5583,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252401</v>
+        <v>131252395</v>
       </c>
       <c r="B50" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5613,10 +5618,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431082</v>
+        <v>431310</v>
       </c>
       <c r="R50" t="n">
-        <v>6779651</v>
+        <v>6779809</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5649,11 +5654,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5680,40 +5680,41 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252322</v>
+        <v>131252337</v>
       </c>
       <c r="B51" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -5723,10 +5724,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431214</v>
+        <v>431622</v>
       </c>
       <c r="R51" t="n">
-        <v>6779702</v>
+        <v>6780061</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5767,6 +5768,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5785,7 +5787,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252337</v>
+        <v>131252352</v>
       </c>
       <c r="B52" t="n">
         <v>8453</v>
@@ -5819,7 +5821,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5829,10 +5831,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431622</v>
+        <v>431374</v>
       </c>
       <c r="R52" t="n">
-        <v>6780061</v>
+        <v>6779783</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5892,7 +5894,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252352</v>
+        <v>131252355</v>
       </c>
       <c r="B53" t="n">
         <v>8453</v>
@@ -5926,7 +5928,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5936,10 +5938,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431374</v>
+        <v>431356</v>
       </c>
       <c r="R53" t="n">
-        <v>6779783</v>
+        <v>6779743</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5999,43 +6001,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252355</v>
+        <v>131252295</v>
       </c>
       <c r="B54" t="n">
-        <v>8453</v>
+        <v>79844</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6043,10 +6039,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431356</v>
+        <v>431735</v>
       </c>
       <c r="R54" t="n">
-        <v>6779743</v>
+        <v>6780060</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6106,10 +6102,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252295</v>
+        <v>131252324</v>
       </c>
       <c r="B55" t="n">
-        <v>79843</v>
+        <v>79012</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6117,37 +6113,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431735</v>
+        <v>431015</v>
       </c>
       <c r="R55" t="n">
-        <v>6780060</v>
+        <v>6779783</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6188,7 +6181,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6207,10 +6199,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252324</v>
+        <v>131252322</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>57889</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6218,34 +6210,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431015</v>
+        <v>431214</v>
       </c>
       <c r="R56" t="n">
-        <v>6779783</v>
+        <v>6779702</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131252376</v>
+        <v>131252397</v>
       </c>
       <c r="B57" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>431316</v>
+        <v>431280</v>
       </c>
       <c r="R57" t="n">
-        <v>6779925</v>
+        <v>6779815</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6401,10 +6401,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131252397</v>
+        <v>131252320</v>
       </c>
       <c r="B58" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6412,34 +6412,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>431280</v>
+        <v>431254</v>
       </c>
       <c r="R58" t="n">
-        <v>6779815</v>
+        <v>6779775</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6501,7 +6509,7 @@
         <v>131252312</v>
       </c>
       <c r="B59" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6603,10 +6611,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131252320</v>
+        <v>131252326</v>
       </c>
       <c r="B60" t="n">
-        <v>57888</v>
+        <v>79012</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6614,31 +6622,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6646,10 +6649,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>431254</v>
+        <v>431339</v>
       </c>
       <c r="R60" t="n">
-        <v>6779775</v>
+        <v>6779765</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6690,6 +6693,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6708,10 +6712,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131252326</v>
+        <v>131252376</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79254</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6719,37 +6723,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>431339</v>
+        <v>431316</v>
       </c>
       <c r="R61" t="n">
-        <v>6779765</v>
+        <v>6779925</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6790,7 +6791,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6809,10 +6809,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131252385</v>
+        <v>131252301</v>
       </c>
       <c r="B62" t="n">
-        <v>79253</v>
+        <v>58051</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6820,34 +6820,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>431690</v>
+        <v>431747</v>
       </c>
       <c r="R62" t="n">
-        <v>6780037</v>
+        <v>6780081</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6906,10 +6914,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131252398</v>
+        <v>131252385</v>
       </c>
       <c r="B63" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6941,10 +6949,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431252</v>
+        <v>431690</v>
       </c>
       <c r="R63" t="n">
-        <v>6779759</v>
+        <v>6780037</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7003,10 +7011,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131252301</v>
+        <v>131252398</v>
       </c>
       <c r="B64" t="n">
-        <v>58050</v>
+        <v>79254</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7014,42 +7022,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431747</v>
+        <v>431252</v>
       </c>
       <c r="R64" t="n">
-        <v>6780081</v>
+        <v>6779759</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7108,37 +7108,43 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131252302</v>
+        <v>131252328</v>
       </c>
       <c r="B65" t="n">
-        <v>91842</v>
+        <v>8453</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7146,10 +7152,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>431364</v>
+        <v>431002</v>
       </c>
       <c r="R65" t="n">
-        <v>6779943</v>
+        <v>6779756</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7209,45 +7215,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131252360</v>
+        <v>131252351</v>
       </c>
       <c r="B66" t="n">
-        <v>79010</v>
+        <v>8453</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>430970</v>
+        <v>431370</v>
       </c>
       <c r="R66" t="n">
-        <v>6779700</v>
+        <v>6779803</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7288,6 +7303,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7306,7 +7322,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131252328</v>
+        <v>131252354</v>
       </c>
       <c r="B67" t="n">
         <v>8453</v>
@@ -7340,7 +7356,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -7350,10 +7366,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>431002</v>
+        <v>431358</v>
       </c>
       <c r="R67" t="n">
-        <v>6779756</v>
+        <v>6779744</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7413,43 +7429,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131252351</v>
+        <v>131252302</v>
       </c>
       <c r="B68" t="n">
-        <v>8453</v>
+        <v>91843</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7457,10 +7467,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>431370</v>
+        <v>431364</v>
       </c>
       <c r="R68" t="n">
-        <v>6779803</v>
+        <v>6779943</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7520,54 +7530,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131252354</v>
+        <v>131252360</v>
       </c>
       <c r="B69" t="n">
-        <v>8453</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>431358</v>
+        <v>430970</v>
       </c>
       <c r="R69" t="n">
-        <v>6779744</v>
+        <v>6779700</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7608,7 +7609,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7627,10 +7627,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131252314</v>
+        <v>131252374</v>
       </c>
       <c r="B70" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7638,42 +7638,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>431448</v>
+        <v>431087</v>
       </c>
       <c r="R70" t="n">
-        <v>6779825</v>
+        <v>6779811</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7732,43 +7724,37 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131252333</v>
+        <v>131252407</v>
       </c>
       <c r="B71" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7776,10 +7762,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>431385</v>
+        <v>430942</v>
       </c>
       <c r="R71" t="n">
-        <v>6779961</v>
+        <v>6779693</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7839,45 +7825,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131252374</v>
+        <v>131252333</v>
       </c>
       <c r="B72" t="n">
-        <v>79253</v>
+        <v>8453</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431087</v>
+        <v>431385</v>
       </c>
       <c r="R72" t="n">
-        <v>6779811</v>
+        <v>6779961</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7918,6 +7913,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7939,7 +7935,7 @@
         <v>131252389</v>
       </c>
       <c r="B73" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8033,10 +8029,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131252407</v>
+        <v>131252375</v>
       </c>
       <c r="B74" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8062,19 +8058,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>430942</v>
+        <v>431294</v>
       </c>
       <c r="R74" t="n">
-        <v>6779693</v>
+        <v>6779898</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8115,7 +8108,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8134,10 +8126,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252375</v>
+        <v>131252314</v>
       </c>
       <c r="B75" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8145,34 +8137,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431294</v>
+        <v>431448</v>
       </c>
       <c r="R75" t="n">
-        <v>6779898</v>
+        <v>6779825</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8231,10 +8231,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131252306</v>
+        <v>131252406</v>
       </c>
       <c r="B76" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8242,42 +8242,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>430985</v>
+        <v>430975</v>
       </c>
       <c r="R76" t="n">
-        <v>6779728</v>
+        <v>6779698</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8339,7 +8331,7 @@
         <v>131252308</v>
       </c>
       <c r="B77" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8441,10 +8433,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252406</v>
+        <v>131252306</v>
       </c>
       <c r="B78" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8452,34 +8444,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430975</v>
+        <v>430985</v>
       </c>
       <c r="R78" t="n">
-        <v>6779698</v>
+        <v>6779728</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8859,10 +8859,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131252383</v>
+        <v>131252315</v>
       </c>
       <c r="B82" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8870,34 +8870,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>431745</v>
+        <v>431370</v>
       </c>
       <c r="R82" t="n">
-        <v>6780081</v>
+        <v>6779803</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8956,10 +8964,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131252379</v>
+        <v>131252383</v>
       </c>
       <c r="B83" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8991,10 +8999,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>431606</v>
+        <v>431745</v>
       </c>
       <c r="R83" t="n">
-        <v>6780065</v>
+        <v>6780081</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9056,7 +9064,7 @@
         <v>131252404</v>
       </c>
       <c r="B84" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9153,7 +9161,7 @@
         <v>131252380</v>
       </c>
       <c r="B85" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9247,10 +9255,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131252315</v>
+        <v>131252379</v>
       </c>
       <c r="B86" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9258,42 +9266,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>431370</v>
+        <v>431606</v>
       </c>
       <c r="R86" t="n">
-        <v>6779803</v>
+        <v>6780065</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9462,7 +9462,7 @@
         <v>131252304</v>
       </c>
       <c r="B88" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>131252323</v>
       </c>
       <c r="B89" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>131252394</v>
       </c>
       <c r="B92" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9976,45 +9976,54 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131252293</v>
+        <v>131252327</v>
       </c>
       <c r="B93" t="n">
-        <v>79872</v>
+        <v>8453</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431669</v>
+        <v>431010</v>
       </c>
       <c r="R93" t="n">
-        <v>6780050</v>
+        <v>6779734</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10055,6 +10064,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10073,53 +10083,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131252300</v>
+        <v>131252293</v>
       </c>
       <c r="B94" t="n">
-        <v>57079</v>
+        <v>79873</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431560</v>
+        <v>431669</v>
       </c>
       <c r="R94" t="n">
-        <v>6779996</v>
+        <v>6780050</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10178,10 +10180,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131252327</v>
+        <v>131252300</v>
       </c>
       <c r="B95" t="n">
-        <v>8453</v>
+        <v>57080</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10189,30 +10191,29 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10222,10 +10223,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431010</v>
+        <v>431560</v>
       </c>
       <c r="R95" t="n">
-        <v>6779734</v>
+        <v>6779996</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10266,7 +10267,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131252378</v>
+        <v>131252382</v>
       </c>
       <c r="B96" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>431561</v>
+        <v>431806</v>
       </c>
       <c r="R96" t="n">
-        <v>6780045</v>
+        <v>6780050</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10382,10 +10382,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131252305</v>
+        <v>131252378</v>
       </c>
       <c r="B97" t="n">
-        <v>91842</v>
+        <v>79254</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10393,37 +10393,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>431438</v>
+        <v>431561</v>
       </c>
       <c r="R97" t="n">
-        <v>6779872</v>
+        <v>6780045</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10464,7 +10461,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10483,10 +10479,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131252388</v>
+        <v>131252305</v>
       </c>
       <c r="B98" t="n">
-        <v>79253</v>
+        <v>91843</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10494,34 +10490,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>431442</v>
+        <v>431438</v>
       </c>
       <c r="R98" t="n">
-        <v>6779937</v>
+        <v>6779872</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10562,6 +10561,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10580,10 +10580,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131252382</v>
+        <v>131252388</v>
       </c>
       <c r="B99" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>431806</v>
+        <v>431442</v>
       </c>
       <c r="R99" t="n">
-        <v>6780050</v>
+        <v>6779937</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -1477,45 +1477,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131252400</v>
+        <v>131252343</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>8453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431231</v>
+        <v>431557</v>
       </c>
       <c r="R10" t="n">
-        <v>6779719</v>
+        <v>6779992</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,6 +1565,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1574,45 +1584,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131252294</v>
+        <v>131252344</v>
       </c>
       <c r="B11" t="n">
-        <v>79873</v>
+        <v>8453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>431192</v>
+        <v>431546</v>
       </c>
       <c r="R11" t="n">
-        <v>6779695</v>
+        <v>6779986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,6 +1672,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1671,7 +1691,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131252343</v>
+        <v>131252358</v>
       </c>
       <c r="B12" t="n">
         <v>8453</v>
@@ -1715,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>431557</v>
+        <v>431077</v>
       </c>
       <c r="R12" t="n">
-        <v>6779992</v>
+        <v>6779648</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,54 +1798,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131252344</v>
+        <v>131252400</v>
       </c>
       <c r="B13" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431546</v>
+        <v>431231</v>
       </c>
       <c r="R13" t="n">
-        <v>6779986</v>
+        <v>6779719</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1866,7 +1877,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1885,54 +1895,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131252358</v>
+        <v>131252294</v>
       </c>
       <c r="B14" t="n">
-        <v>8453</v>
+        <v>79873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431077</v>
+        <v>431192</v>
       </c>
       <c r="R14" t="n">
-        <v>6779648</v>
+        <v>6779695</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,7 +1974,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131252403</v>
+        <v>131252316</v>
       </c>
       <c r="B32" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3735,34 +3735,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>431055</v>
+        <v>431357</v>
       </c>
       <c r="R32" t="n">
-        <v>6779612</v>
+        <v>6779763</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3795,11 +3803,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3826,45 +3829,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131252384</v>
+        <v>131252346</v>
       </c>
       <c r="B33" t="n">
-        <v>79254</v>
+        <v>8453</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>431710</v>
+        <v>431434</v>
       </c>
       <c r="R33" t="n">
-        <v>6780009</v>
+        <v>6779875</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3899,17 +3911,13 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 50 m.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3928,7 +3936,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131252346</v>
+        <v>131252357</v>
       </c>
       <c r="B34" t="n">
         <v>8453</v>
@@ -3972,10 +3980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>431434</v>
+        <v>431074</v>
       </c>
       <c r="R34" t="n">
-        <v>6779875</v>
+        <v>6779685</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4035,54 +4043,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131252414</v>
+        <v>131252403</v>
       </c>
       <c r="B35" t="n">
-        <v>8442</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>431245</v>
+        <v>431055</v>
       </c>
       <c r="R35" t="n">
-        <v>6779803</v>
+        <v>6779612</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4117,13 +4116,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4142,54 +4145,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131252357</v>
+        <v>131252384</v>
       </c>
       <c r="B36" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>431074</v>
+        <v>431710</v>
       </c>
       <c r="R36" t="n">
-        <v>6779685</v>
+        <v>6780009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4224,13 +4218,17 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 50 m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4249,37 +4247,43 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131252325</v>
+        <v>131252414</v>
       </c>
       <c r="B37" t="n">
-        <v>79012</v>
+        <v>8442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>106554</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4287,10 +4291,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>431743</v>
+        <v>431245</v>
       </c>
       <c r="R37" t="n">
-        <v>6780091</v>
+        <v>6779803</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4350,10 +4354,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131252316</v>
+        <v>131252325</v>
       </c>
       <c r="B38" t="n">
-        <v>57889</v>
+        <v>79012</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4361,31 +4365,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4393,10 +4392,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>431357</v>
+        <v>431743</v>
       </c>
       <c r="R38" t="n">
-        <v>6779763</v>
+        <v>6780091</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4437,6 +4436,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131252341</v>
+        <v>131252339</v>
       </c>
       <c r="B43" t="n">
         <v>8453</v>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>431684</v>
+        <v>431754</v>
       </c>
       <c r="R43" t="n">
-        <v>6780041</v>
+        <v>6780143</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4958,7 +4958,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131252339</v>
+        <v>131252341</v>
       </c>
       <c r="B44" t="n">
         <v>8453</v>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>431754</v>
+        <v>431684</v>
       </c>
       <c r="R44" t="n">
-        <v>6780143</v>
+        <v>6780041</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131252401</v>
+        <v>131252322</v>
       </c>
       <c r="B49" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5492,34 +5492,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>431082</v>
+        <v>431214</v>
       </c>
       <c r="R49" t="n">
-        <v>6779651</v>
+        <v>6779702</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5552,11 +5560,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5583,10 +5586,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131252395</v>
+        <v>131252295</v>
       </c>
       <c r="B50" t="n">
-        <v>79254</v>
+        <v>79844</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5594,34 +5597,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>431310</v>
+        <v>431735</v>
       </c>
       <c r="R50" t="n">
-        <v>6779809</v>
+        <v>6780060</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5662,6 +5668,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5680,54 +5687,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131252337</v>
+        <v>131252324</v>
       </c>
       <c r="B51" t="n">
-        <v>8453</v>
+        <v>79012</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>431622</v>
+        <v>431015</v>
       </c>
       <c r="R51" t="n">
-        <v>6780061</v>
+        <v>6779783</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5768,7 +5766,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5787,7 +5784,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131252352</v>
+        <v>131252337</v>
       </c>
       <c r="B52" t="n">
         <v>8453</v>
@@ -5821,7 +5818,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5831,10 +5828,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>431374</v>
+        <v>431622</v>
       </c>
       <c r="R52" t="n">
-        <v>6779783</v>
+        <v>6780061</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5894,7 +5891,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131252355</v>
+        <v>131252352</v>
       </c>
       <c r="B53" t="n">
         <v>8453</v>
@@ -5928,7 +5925,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -5938,10 +5935,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>431356</v>
+        <v>431374</v>
       </c>
       <c r="R53" t="n">
-        <v>6779743</v>
+        <v>6779783</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6001,37 +5998,43 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131252295</v>
+        <v>131252355</v>
       </c>
       <c r="B54" t="n">
-        <v>79844</v>
+        <v>8453</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6039,10 +6042,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>431735</v>
+        <v>431356</v>
       </c>
       <c r="R54" t="n">
-        <v>6780060</v>
+        <v>6779743</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6102,10 +6105,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131252324</v>
+        <v>131252401</v>
       </c>
       <c r="B55" t="n">
-        <v>79012</v>
+        <v>79254</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6113,21 +6116,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6137,10 +6140,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>431015</v>
+        <v>431082</v>
       </c>
       <c r="R55" t="n">
-        <v>6779783</v>
+        <v>6779651</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6173,6 +6176,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6199,10 +6207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131252322</v>
+        <v>131252395</v>
       </c>
       <c r="B56" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6210,42 +6218,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>431214</v>
+        <v>431310</v>
       </c>
       <c r="R56" t="n">
-        <v>6779702</v>
+        <v>6779809</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131252385</v>
+        <v>131252398</v>
       </c>
       <c r="B63" t="n">
         <v>79254</v>
@@ -6949,10 +6949,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>431690</v>
+        <v>431252</v>
       </c>
       <c r="R63" t="n">
-        <v>6780037</v>
+        <v>6779759</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7011,7 +7011,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131252398</v>
+        <v>131252385</v>
       </c>
       <c r="B64" t="n">
         <v>79254</v>
@@ -7046,10 +7046,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>431252</v>
+        <v>431690</v>
       </c>
       <c r="R64" t="n">
-        <v>6779759</v>
+        <v>6780037</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131252407</v>
+        <v>131252389</v>
       </c>
       <c r="B71" t="n">
         <v>79254</v>
@@ -7753,19 +7753,16 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>430942</v>
+        <v>431389</v>
       </c>
       <c r="R71" t="n">
-        <v>6779693</v>
+        <v>6779928</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7806,7 +7803,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7825,54 +7821,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131252333</v>
+        <v>131252375</v>
       </c>
       <c r="B72" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>431385</v>
+        <v>431294</v>
       </c>
       <c r="R72" t="n">
-        <v>6779961</v>
+        <v>6779898</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7913,7 +7900,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7932,10 +7918,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131252389</v>
+        <v>131252314</v>
       </c>
       <c r="B73" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7943,34 +7929,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>431389</v>
+        <v>431448</v>
       </c>
       <c r="R73" t="n">
-        <v>6779928</v>
+        <v>6779825</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8029,7 +8023,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131252375</v>
+        <v>131252407</v>
       </c>
       <c r="B74" t="n">
         <v>79254</v>
@@ -8058,16 +8052,19 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>431294</v>
+        <v>430942</v>
       </c>
       <c r="R74" t="n">
-        <v>6779898</v>
+        <v>6779693</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8108,6 +8105,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8126,40 +8124,41 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131252314</v>
+        <v>131252333</v>
       </c>
       <c r="B75" t="n">
-        <v>57889</v>
+        <v>8453</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -8169,10 +8168,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>431448</v>
+        <v>431385</v>
       </c>
       <c r="R75" t="n">
-        <v>6779825</v>
+        <v>6779961</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8213,6 +8212,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8328,7 +8328,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131252308</v>
+        <v>131252306</v>
       </c>
       <c r="B77" t="n">
         <v>57889</v>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>431243</v>
+        <v>430985</v>
       </c>
       <c r="R77" t="n">
-        <v>6779888</v>
+        <v>6779728</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8433,40 +8433,41 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131252306</v>
+        <v>131252347</v>
       </c>
       <c r="B78" t="n">
-        <v>57889</v>
+        <v>8453</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -8476,10 +8477,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>430985</v>
+        <v>431446</v>
       </c>
       <c r="R78" t="n">
-        <v>6779728</v>
+        <v>6779877</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8520,6 +8521,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8538,7 +8540,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131252347</v>
+        <v>131252349</v>
       </c>
       <c r="B79" t="n">
         <v>8453</v>
@@ -8572,7 +8574,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8582,10 +8584,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>431446</v>
+        <v>431444</v>
       </c>
       <c r="R79" t="n">
-        <v>6779877</v>
+        <v>6779818</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8645,7 +8647,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131252349</v>
+        <v>131252345</v>
       </c>
       <c r="B80" t="n">
         <v>8453</v>
@@ -8679,7 +8681,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8689,10 +8691,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>431444</v>
+        <v>431376</v>
       </c>
       <c r="R80" t="n">
-        <v>6779818</v>
+        <v>6779903</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8752,41 +8754,40 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131252345</v>
+        <v>131252308</v>
       </c>
       <c r="B81" t="n">
-        <v>8453</v>
+        <v>57889</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8796,10 +8797,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>431376</v>
+        <v>431243</v>
       </c>
       <c r="R81" t="n">
-        <v>6779903</v>
+        <v>6779888</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,7 +8841,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9665,54 +9665,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131252331</v>
+        <v>131252394</v>
       </c>
       <c r="B90" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>431291</v>
+        <v>431327</v>
       </c>
       <c r="R90" t="n">
-        <v>6779892</v>
+        <v>6779796</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9753,7 +9744,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9772,7 +9762,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131252330</v>
+        <v>131252331</v>
       </c>
       <c r="B91" t="n">
         <v>8453</v>
@@ -9816,10 +9806,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>431075</v>
+        <v>431291</v>
       </c>
       <c r="R91" t="n">
-        <v>6779775</v>
+        <v>6779892</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9879,45 +9869,54 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131252394</v>
+        <v>131252330</v>
       </c>
       <c r="B92" t="n">
-        <v>79254</v>
+        <v>8453</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>431327</v>
+        <v>431075</v>
       </c>
       <c r="R92" t="n">
-        <v>6779796</v>
+        <v>6779775</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9958,6 +9957,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9976,54 +9976,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131252327</v>
+        <v>131252293</v>
       </c>
       <c r="B93" t="n">
-        <v>8453</v>
+        <v>79873</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>431010</v>
+        <v>431669</v>
       </c>
       <c r="R93" t="n">
-        <v>6779734</v>
+        <v>6780050</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10064,7 +10055,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10083,45 +10073,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131252293</v>
+        <v>131252300</v>
       </c>
       <c r="B94" t="n">
-        <v>79873</v>
+        <v>57080</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Getdöden, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>431669</v>
+        <v>431560</v>
       </c>
       <c r="R94" t="n">
-        <v>6780050</v>
+        <v>6779996</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10180,10 +10178,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131252300</v>
+        <v>131252327</v>
       </c>
       <c r="B95" t="n">
-        <v>57080</v>
+        <v>8453</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10191,29 +10189,30 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10223,10 +10222,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>431560</v>
+        <v>431010</v>
       </c>
       <c r="R95" t="n">
-        <v>6779996</v>
+        <v>6779734</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10267,6 +10266,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7021-2026 artfynd.xlsx
+++ b/artfynd/A 7021-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AZ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252302</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252303</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252304</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252370</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252371</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252372</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1464,6 +1504,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252373</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252374</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1658,6 +1708,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252375</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252376</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252377</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252378</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252379</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2143,6 +2218,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252380</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252381</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252382</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252383</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252384</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252385</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2734,6 +2839,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252386</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252387</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252388</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252389</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252390</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252391</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,6 +3451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252392</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3413,6 +3553,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252393</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3510,6 +3655,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252394</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3607,6 +3757,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252395</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3704,6 +3859,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252396</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3801,6 +3961,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252397</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3898,6 +4063,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252398</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3995,6 +4165,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252399</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4092,6 +4267,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252400</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4194,6 +4374,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252401</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4295,6 +4480,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252402</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4397,6 +4587,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252403</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4494,6 +4689,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252404</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4596,6 +4796,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252405</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4693,6 +4898,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252406</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4794,6 +5004,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252407</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4891,6 +5106,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252408</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4988,6 +5208,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252359</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5085,6 +5310,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252360</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5182,6 +5412,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252293</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5279,6 +5514,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252294</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5384,6 +5624,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252306</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5489,6 +5734,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252307</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5594,6 +5844,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252308</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5699,6 +5954,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252309</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5804,6 +6064,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252310</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5909,6 +6174,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252311</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6014,6 +6284,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252312</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6119,6 +6394,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252313</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6224,6 +6504,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252314</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6329,6 +6614,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252315</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6434,6 +6724,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252316</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6539,6 +6834,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252317</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6644,6 +6944,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252319</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6749,6 +7054,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252320</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6854,6 +7164,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252321</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6959,6 +7274,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252322</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7064,6 +7384,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252323</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7169,6 +7494,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252298</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7274,6 +7604,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252300</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7381,6 +7716,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252409</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7486,6 +7826,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252301</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7593,6 +7938,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252327</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7700,6 +8050,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252328</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7807,6 +8162,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252329</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7914,6 +8274,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252330</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8021,6 +8386,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252331</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8128,6 +8498,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252332</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8235,6 +8610,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252333</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8342,6 +8722,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252334</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8449,6 +8834,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252335</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8556,6 +8946,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252336</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8663,6 +9058,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252337</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8770,6 +9170,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252338</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8877,6 +9282,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252339</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8984,6 +9394,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252340</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9091,6 +9506,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252341</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9198,6 +9618,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252342</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9305,6 +9730,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252343</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9412,6 +9842,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252344</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9519,6 +9954,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252345</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9626,6 +10066,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252346</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9733,6 +10178,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252347</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9840,6 +10290,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252348</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9947,6 +10402,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252349</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10054,6 +10514,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252350</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10161,6 +10626,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252351</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10268,6 +10738,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252352</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10375,6 +10850,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252353</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10482,6 +10962,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252354</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10589,6 +11074,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252355</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10696,6 +11186,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252356</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10803,6 +11298,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252357</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10910,6 +11410,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252358</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11017,6 +11522,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252413</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11124,6 +11634,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252414</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11221,6 +11736,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252324</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11322,6 +11842,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252325</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11423,6 +11948,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252326</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11524,8 +12054,121 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131252295</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>